--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -16,8 +16,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">专项检查!$A$1:$B$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$28</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$308</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$29</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$312</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">问题汇总!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="958">
   <si>
     <r>
       <rPr>
@@ -17504,6 +17504,181 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">not blinded … the 15 index examinations of the excluded children included 10 labeled positive (UGI series 6 of 7, CT 4 of 7, ultrasound 0 of 1) … 64 of 118 (54.2%) rather than 64 of 117 (54.7%)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【一致】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">核对表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">现有检出标签</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列：排除者索引检查 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次，阳性 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UGI 6/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CT 4/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、超声 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64/118 = 54.24%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64/117 = 54.70%</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -30949,7 +31124,7 @@
     <t xml:space="preserve">Title Page · Word count</t>
   </si>
   <si>
-    <t xml:space="preserve">2,989 … Abstract: 249 words</t>
+    <t xml:space="preserve">2,995 … Abstract: 249 words</t>
   </si>
   <si>
     <r>
@@ -30984,7 +31159,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2989</t>
+      <t xml:space="preserve">2995</t>
     </r>
     <r>
       <rPr>
@@ -31107,7 +31282,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Word count: 2,989 … Tables: 4; Figures: 3; Supplements 1–4</t>
+    <t xml:space="preserve">Word count: 2,995 … Tables: 4; Figures: 3; Supplements 1–4</t>
   </si>
   <si>
     <r>
@@ -31125,7 +31300,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2989</t>
+      <t xml:space="preserve">2995</t>
     </r>
   </si>
   <si>
@@ -31374,6 +31549,36 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">研究对象（计数词）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> One author</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方法 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">索引检查（计数词）</t>
     </r>
   </si>
@@ -32266,6 +32471,235 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">1 · K1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（计数词）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> one negative</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">； </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">one question</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">by one of</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 · K2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（计数词）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> One same</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">； </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Three same</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">； </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">one child</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">； </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">one examination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">； </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">three reports</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">by one of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">in one child</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">one in</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">2 · </t>
     </r>
     <r>
@@ -36369,6 +36803,404 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方法 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">研究对象；补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 · K1–K3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Title Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（复核分工）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">All operative records were re-read for 34 children …</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K1–K3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未写复核者</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">One author, with the imaging labels visible, re-read …</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">补</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非盲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">及排除方向核查；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">K3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">写明复核者为作者；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Title Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">贡献补 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KZ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ZM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的复核分工</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用户 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">告知：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S1 Haiyan Lei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S2 Kai Zheng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、超声阅读者 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Zhengliang Meng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（甲）与 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Jun Shu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（乙）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">核对表显示了现有检出标签，故如实写为非盲</t>
     </r>
   </si>
   <si>
@@ -37296,7 +38128,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(核对表!B2:B2000)</f>
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37305,7 +38137,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(核对表!C2:C2000,"【一致】*")</f>
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37341,7 +38173,7 @@
       </c>
       <c r="B26" s="6" t="n">
         <f aca="false">COUNTIF(核对表!C2:C2000,"【定义/描述性数字】*")</f>
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37369,7 +38201,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E308"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -39962,15 +40794,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="B153" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="B153" s="9" t="s">
+      <c r="C153" s="8" t="s">
         <v>420</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>421</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>31</v>
@@ -39979,15 +40811,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B154" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="B154" s="9" t="s">
+      <c r="C154" s="8" t="s">
         <v>423</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>424</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>31</v>
@@ -39996,15 +40828,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="B155" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="B155" s="9" t="s">
+      <c r="C155" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>401</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>31</v>
@@ -40021,7 +40853,7 @@
         <v>428</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>31</v>
@@ -40030,9 +40862,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B157" s="9" t="s">
         <v>430</v>
@@ -40047,15 +40879,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="B158" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="B158" s="9" t="s">
+      <c r="C158" s="8" t="s">
         <v>433</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>434</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>31</v>
@@ -40066,7 +40898,7 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B159" s="9" t="s">
         <v>435</v>
@@ -40083,13 +40915,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="B160" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="C160" s="8" t="s">
         <v>438</v>
-      </c>
-      <c r="C160" s="8" t="s">
-        <v>439</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>31</v>
@@ -40100,13 +40932,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B161" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="B161" s="9" t="s">
+      <c r="C161" s="8" t="s">
         <v>441</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>442</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>31</v>
@@ -40117,13 +40949,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="B162" s="9" t="s">
         <v>443</v>
       </c>
-      <c r="B162" s="9" t="s">
+      <c r="C162" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>31</v>
@@ -40132,15 +40964,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="B163" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="B163" s="9" t="s">
+      <c r="C163" s="8" t="s">
         <v>447</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>448</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>31</v>
@@ -40149,15 +40981,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B164" s="9" t="s">
         <v>449</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="C164" s="8" t="s">
         <v>450</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>451</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>31</v>
@@ -40168,13 +41000,13 @@
     </row>
     <row r="165" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B165" s="9" t="s">
         <v>452</v>
       </c>
-      <c r="B165" s="9" t="s">
+      <c r="C165" s="8" t="s">
         <v>453</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>454</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>31</v>
@@ -40185,13 +41017,13 @@
     </row>
     <row r="166" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B166" s="9" t="s">
         <v>455</v>
       </c>
-      <c r="B166" s="9" t="s">
+      <c r="C166" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>457</v>
       </c>
       <c r="D166" s="8" t="s">
         <v>31</v>
@@ -40200,9 +41032,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="8" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B167" s="9" t="s">
         <v>458</v>
@@ -40217,15 +41049,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B168" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="B168" s="9" t="s">
+      <c r="C168" s="8" t="s">
         <v>461</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>462</v>
       </c>
       <c r="D168" s="8" t="s">
         <v>31</v>
@@ -40236,7 +41068,7 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B169" s="9" t="s">
         <v>463</v>
@@ -40251,15 +41083,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="B170" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="B170" s="9" t="s">
+      <c r="C170" s="8" t="s">
         <v>466</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>467</v>
       </c>
       <c r="D170" s="8" t="s">
         <v>31</v>
@@ -40268,32 +41100,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="B171" s="11" t="s">
+    <row r="171" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="B171" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="C171" s="10" t="s">
+      <c r="C171" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="D171" s="10" t="s">
+      <c r="D171" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E171" s="10" t="s">
+      <c r="E171" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B172" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="B172" s="11" t="s">
+      <c r="C172" s="10" t="s">
         <v>471</v>
-      </c>
-      <c r="C172" s="10" t="s">
-        <v>367</v>
       </c>
       <c r="D172" s="10" t="s">
         <v>31</v>
@@ -40302,66 +41134,66 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="8" t="s">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="B173" s="9" t="s">
+      <c r="B173" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="C173" s="8" t="s">
+      <c r="C173" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D173" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E173" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="D173" s="8" t="s">
+      <c r="B174" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="D174" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E173" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="B174" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="C174" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="D174" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E174" s="10" t="s">
+      <c r="E174" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="B175" s="9" t="s">
+      <c r="A175" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="B175" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="D175" s="8" t="s">
+      <c r="D175" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E175" s="8" t="s">
+      <c r="E175" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B176" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="B176" s="9" t="s">
+      <c r="C176" s="8" t="s">
         <v>481</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>482</v>
       </c>
       <c r="D176" s="8" t="s">
         <v>31</v>
@@ -40370,15 +41202,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="B177" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="B177" s="9" t="s">
+      <c r="C177" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>485</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>31</v>
@@ -40387,49 +41219,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="10" t="s">
+    <row r="178" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="B178" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="B178" s="11" t="s">
+      <c r="C178" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B179" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="C178" s="10" t="s">
+      <c r="C179" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="D178" s="10" t="s">
+      <c r="D179" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E178" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="179" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="B179" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="D179" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E179" s="8" t="s">
+      <c r="E179" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="B180" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="B180" s="9" t="s">
+      <c r="C180" s="8" t="s">
         <v>491</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="D180" s="8" t="s">
         <v>31</v>
@@ -40440,10 +41272,10 @@
     </row>
     <row r="181" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="B181" s="9" t="s">
         <v>493</v>
-      </c>
-      <c r="B181" s="9" t="s">
-        <v>488</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>494</v>
@@ -40455,15 +41287,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="8" t="s">
         <v>495</v>
       </c>
       <c r="B182" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C182" s="8" t="s">
         <v>496</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>497</v>
       </c>
       <c r="D182" s="8" t="s">
         <v>31</v>
@@ -40474,13 +41306,13 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B183" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="B183" s="9" t="s">
+      <c r="C183" s="8" t="s">
         <v>499</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>500</v>
       </c>
       <c r="D183" s="8" t="s">
         <v>31</v>
@@ -40491,10 +41323,10 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B184" s="9" t="s">
         <v>501</v>
-      </c>
-      <c r="B184" s="9" t="s">
-        <v>491</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>502</v>
@@ -40506,15 +41338,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="8" t="s">
         <v>503</v>
       </c>
       <c r="B185" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C185" s="8" t="s">
         <v>504</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="D185" s="8" t="s">
         <v>31</v>
@@ -40523,15 +41355,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="B186" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="C186" s="8" t="s">
         <v>507</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>508</v>
       </c>
       <c r="D186" s="8" t="s">
         <v>31</v>
@@ -40542,13 +41374,13 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="B187" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="B187" s="9" t="s">
+      <c r="C187" s="8" t="s">
         <v>510</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>511</v>
       </c>
       <c r="D187" s="8" t="s">
         <v>31</v>
@@ -40557,15 +41389,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B188" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="B188" s="9" t="s">
+      <c r="C188" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>514</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>31</v>
@@ -40576,13 +41408,13 @@
     </row>
     <row r="189" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="B189" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="B189" s="9" t="s">
-        <v>491</v>
-      </c>
       <c r="C189" s="8" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="D189" s="8" t="s">
         <v>31</v>
@@ -40591,15 +41423,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="8" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="D190" s="8" t="s">
         <v>31</v>
@@ -40609,48 +41441,48 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="10" t="s">
+      <c r="A191" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B191" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="C191" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="C191" s="10" t="s">
+      <c r="D191" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="D191" s="10" t="s">
+      <c r="B192" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="D192" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E191" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="B192" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="C192" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="D192" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E192" s="8" t="s">
+      <c r="E192" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B193" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="C193" s="8" t="s">
         <v>526</v>
-      </c>
-      <c r="C193" s="8" t="s">
-        <v>527</v>
       </c>
       <c r="D193" s="8" t="s">
         <v>31</v>
@@ -40661,13 +41493,13 @@
     </row>
     <row r="194" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="B194" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="B194" s="9" t="s">
+      <c r="C194" s="8" t="s">
         <v>529</v>
-      </c>
-      <c r="C194" s="8" t="s">
-        <v>530</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>31</v>
@@ -40678,13 +41510,13 @@
     </row>
     <row r="195" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="B195" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="C195" s="8" t="s">
         <v>532</v>
-      </c>
-      <c r="C195" s="8" t="s">
-        <v>533</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>31</v>
@@ -40695,13 +41527,13 @@
     </row>
     <row r="196" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="B196" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="B196" s="9" t="s">
-        <v>526</v>
-      </c>
       <c r="C196" s="8" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>31</v>
@@ -40712,13 +41544,13 @@
     </row>
     <row r="197" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>31</v>
@@ -40729,13 +41561,13 @@
     </row>
     <row r="198" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="B198" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="B198" s="9" t="s">
+      <c r="C198" s="8" t="s">
         <v>539</v>
-      </c>
-      <c r="C198" s="8" t="s">
-        <v>540</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>31</v>
@@ -40746,13 +41578,13 @@
     </row>
     <row r="199" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="B199" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="B199" s="9" t="s">
-        <v>526</v>
-      </c>
       <c r="C199" s="8" t="s">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="D199" s="8" t="s">
         <v>31</v>
@@ -40763,13 +41595,13 @@
     </row>
     <row r="200" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="8" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="D200" s="8" t="s">
         <v>31</v>
@@ -40780,13 +41612,13 @@
     </row>
     <row r="201" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="B201" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="B201" s="9" t="s">
+      <c r="C201" s="8" t="s">
         <v>546</v>
-      </c>
-      <c r="C201" s="8" t="s">
-        <v>547</v>
       </c>
       <c r="D201" s="8" t="s">
         <v>31</v>
@@ -40797,13 +41629,13 @@
     </row>
     <row r="202" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="B202" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="B202" s="9" t="s">
+      <c r="C202" s="8" t="s">
         <v>549</v>
-      </c>
-      <c r="C202" s="8" t="s">
-        <v>550</v>
       </c>
       <c r="D202" s="8" t="s">
         <v>31</v>
@@ -40814,13 +41646,13 @@
     </row>
     <row r="203" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="B203" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="B203" s="9" t="s">
+      <c r="C203" s="8" t="s">
         <v>552</v>
-      </c>
-      <c r="C203" s="8" t="s">
-        <v>553</v>
       </c>
       <c r="D203" s="8" t="s">
         <v>31</v>
@@ -40829,15 +41661,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="B204" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="B204" s="9" t="s">
+      <c r="C204" s="8" t="s">
         <v>555</v>
-      </c>
-      <c r="C204" s="8" t="s">
-        <v>556</v>
       </c>
       <c r="D204" s="8" t="s">
         <v>31</v>
@@ -40848,13 +41680,13 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="B205" s="9" t="s">
         <v>557</v>
       </c>
-      <c r="B205" s="9" t="s">
+      <c r="C205" s="8" t="s">
         <v>558</v>
-      </c>
-      <c r="C205" s="8" t="s">
-        <v>559</v>
       </c>
       <c r="D205" s="8" t="s">
         <v>31</v>
@@ -40865,13 +41697,13 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B206" s="9" t="s">
         <v>560</v>
       </c>
-      <c r="B206" s="9" t="s">
+      <c r="C206" s="8" t="s">
         <v>561</v>
-      </c>
-      <c r="C206" s="8" t="s">
-        <v>562</v>
       </c>
       <c r="D206" s="8" t="s">
         <v>31</v>
@@ -40880,15 +41712,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="B207" s="9" t="s">
         <v>563</v>
       </c>
-      <c r="B207" s="9" t="s">
+      <c r="C207" s="8" t="s">
         <v>564</v>
-      </c>
-      <c r="C207" s="8" t="s">
-        <v>565</v>
       </c>
       <c r="D207" s="8" t="s">
         <v>31</v>
@@ -40897,15 +41729,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="B208" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="B208" s="9" t="s">
+      <c r="C208" s="8" t="s">
         <v>567</v>
-      </c>
-      <c r="C208" s="8" t="s">
-        <v>568</v>
       </c>
       <c r="D208" s="8" t="s">
         <v>31</v>
@@ -40914,15 +41746,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="B209" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="B209" s="9" t="s">
+      <c r="C209" s="8" t="s">
         <v>570</v>
-      </c>
-      <c r="C209" s="8" t="s">
-        <v>571</v>
       </c>
       <c r="D209" s="8" t="s">
         <v>31</v>
@@ -40931,15 +41763,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B210" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="B210" s="9" t="s">
+      <c r="C210" s="8" t="s">
         <v>573</v>
-      </c>
-      <c r="C210" s="8" t="s">
-        <v>574</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>31</v>
@@ -40950,13 +41782,13 @@
     </row>
     <row r="211" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="B211" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="B211" s="9" t="s">
+      <c r="C211" s="8" t="s">
         <v>576</v>
-      </c>
-      <c r="C211" s="8" t="s">
-        <v>577</v>
       </c>
       <c r="D211" s="8" t="s">
         <v>31</v>
@@ -40965,15 +41797,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B212" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="B212" s="9" t="s">
+      <c r="C212" s="8" t="s">
         <v>579</v>
-      </c>
-      <c r="C212" s="8" t="s">
-        <v>580</v>
       </c>
       <c r="D212" s="8" t="s">
         <v>31</v>
@@ -40982,15 +41814,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="B213" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="B213" s="9" t="s">
+      <c r="C213" s="8" t="s">
         <v>582</v>
-      </c>
-      <c r="C213" s="8" t="s">
-        <v>583</v>
       </c>
       <c r="D213" s="8" t="s">
         <v>31</v>
@@ -41001,13 +41833,13 @@
     </row>
     <row r="214" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="B214" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="C214" s="8" t="s">
         <v>585</v>
-      </c>
-      <c r="C214" s="8" t="s">
-        <v>586</v>
       </c>
       <c r="D214" s="8" t="s">
         <v>31</v>
@@ -41018,13 +41850,13 @@
     </row>
     <row r="215" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="B215" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="C215" s="8" t="s">
         <v>588</v>
-      </c>
-      <c r="C215" s="8" t="s">
-        <v>589</v>
       </c>
       <c r="D215" s="8" t="s">
         <v>31</v>
@@ -41033,49 +41865,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="B216" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="B216" s="9" t="s">
-        <v>585</v>
-      </c>
       <c r="C216" s="8" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>591</v>
+        <v>31</v>
       </c>
       <c r="E216" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="8" t="s">
         <v>592</v>
       </c>
+      <c r="B217" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="C217" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="D217" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>594</v>
+      </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="C217" s="8" t="s">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="D217" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E217" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="8" t="s">
+      <c r="B218" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="C218" s="8" t="s">
         <v>597</v>
-      </c>
-      <c r="C218" s="8" t="s">
-        <v>598</v>
       </c>
       <c r="D218" s="8" t="s">
         <v>31</v>
@@ -41086,13 +41918,13 @@
     </row>
     <row r="219" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="B219" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="B219" s="9" t="s">
+      <c r="C219" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C219" s="8" t="s">
-        <v>601</v>
       </c>
       <c r="D219" s="8" t="s">
         <v>31</v>
@@ -41103,13 +41935,13 @@
     </row>
     <row r="220" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="B220" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="B220" s="9" t="s">
+      <c r="C220" s="8" t="s">
         <v>603</v>
-      </c>
-      <c r="C220" s="8" t="s">
-        <v>604</v>
       </c>
       <c r="D220" s="8" t="s">
         <v>31</v>
@@ -41120,13 +41952,13 @@
     </row>
     <row r="221" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="B221" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="B221" s="9" t="s">
+      <c r="C221" s="8" t="s">
         <v>606</v>
-      </c>
-      <c r="C221" s="8" t="s">
-        <v>607</v>
       </c>
       <c r="D221" s="8" t="s">
         <v>31</v>
@@ -41137,13 +41969,13 @@
     </row>
     <row r="222" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="B222" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="C222" s="8" t="s">
         <v>609</v>
-      </c>
-      <c r="C222" s="8" t="s">
-        <v>610</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>31</v>
@@ -41154,13 +41986,13 @@
     </row>
     <row r="223" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="B223" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="C223" s="8" t="s">
         <v>612</v>
-      </c>
-      <c r="C223" s="8" t="s">
-        <v>613</v>
       </c>
       <c r="D223" s="8" t="s">
         <v>31</v>
@@ -41171,13 +42003,13 @@
     </row>
     <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="B224" s="9" t="s">
         <v>614</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="C224" s="8" t="s">
         <v>615</v>
-      </c>
-      <c r="C224" s="8" t="s">
-        <v>616</v>
       </c>
       <c r="D224" s="8" t="s">
         <v>31</v>
@@ -41186,15 +42018,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B225" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="C225" s="8" t="s">
         <v>618</v>
-      </c>
-      <c r="C225" s="8" t="s">
-        <v>619</v>
       </c>
       <c r="D225" s="8" t="s">
         <v>31</v>
@@ -41203,15 +42035,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B226" s="9" t="s">
         <v>620</v>
       </c>
-      <c r="B226" s="9" t="s">
+      <c r="C226" s="8" t="s">
         <v>621</v>
-      </c>
-      <c r="C226" s="8" t="s">
-        <v>622</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>31</v>
@@ -41222,13 +42054,13 @@
     </row>
     <row r="227" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B227" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="B227" s="9" t="s">
+      <c r="C227" s="8" t="s">
         <v>624</v>
-      </c>
-      <c r="C227" s="8" t="s">
-        <v>625</v>
       </c>
       <c r="D227" s="8" t="s">
         <v>31</v>
@@ -41239,13 +42071,13 @@
     </row>
     <row r="228" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B228" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="B228" s="9" t="s">
+      <c r="C228" s="8" t="s">
         <v>627</v>
-      </c>
-      <c r="C228" s="8" t="s">
-        <v>628</v>
       </c>
       <c r="D228" s="8" t="s">
         <v>31</v>
@@ -41256,13 +42088,13 @@
     </row>
     <row r="229" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="B229" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="B229" s="9" t="s">
+      <c r="C229" s="8" t="s">
         <v>630</v>
-      </c>
-      <c r="C229" s="8" t="s">
-        <v>631</v>
       </c>
       <c r="D229" s="8" t="s">
         <v>31</v>
@@ -41273,13 +42105,13 @@
     </row>
     <row r="230" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B230" s="9" t="s">
         <v>632</v>
       </c>
-      <c r="B230" s="9" t="s">
+      <c r="C230" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="C230" s="8" t="s">
-        <v>634</v>
       </c>
       <c r="D230" s="8" t="s">
         <v>31</v>
@@ -41290,13 +42122,13 @@
     </row>
     <row r="231" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="B231" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="B231" s="9" t="s">
+      <c r="C231" s="8" t="s">
         <v>636</v>
-      </c>
-      <c r="C231" s="8" t="s">
-        <v>637</v>
       </c>
       <c r="D231" s="8" t="s">
         <v>31</v>
@@ -41307,13 +42139,13 @@
     </row>
     <row r="232" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="B232" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="B232" s="9" t="s">
+      <c r="C232" s="8" t="s">
         <v>639</v>
-      </c>
-      <c r="C232" s="8" t="s">
-        <v>640</v>
       </c>
       <c r="D232" s="8" t="s">
         <v>31</v>
@@ -41324,13 +42156,13 @@
     </row>
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="B233" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="B233" s="9" t="s">
+      <c r="C233" s="8" t="s">
         <v>642</v>
-      </c>
-      <c r="C233" s="8" t="s">
-        <v>643</v>
       </c>
       <c r="D233" s="8" t="s">
         <v>31</v>
@@ -41341,13 +42173,13 @@
     </row>
     <row r="234" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B234" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="B234" s="9" t="s">
+      <c r="C234" s="8" t="s">
         <v>645</v>
-      </c>
-      <c r="C234" s="8" t="s">
-        <v>646</v>
       </c>
       <c r="D234" s="8" t="s">
         <v>31</v>
@@ -41356,15 +42188,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="B235" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="B235" s="9" t="s">
+      <c r="C235" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="C235" s="8" t="s">
-        <v>649</v>
       </c>
       <c r="D235" s="8" t="s">
         <v>31</v>
@@ -41375,13 +42207,13 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="B236" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="B236" s="8" t="s">
+      <c r="C236" s="8" t="s">
         <v>651</v>
-      </c>
-      <c r="C236" s="8" t="s">
-        <v>652</v>
       </c>
       <c r="D236" s="8" t="s">
         <v>31</v>
@@ -41392,10 +42224,10 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="B237" s="8" t="s">
         <v>653</v>
-      </c>
-      <c r="B237" s="8" t="s">
-        <v>651</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>654</v>
@@ -41412,7 +42244,7 @@
         <v>655</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C238" s="8" t="s">
         <v>656</v>
@@ -41424,15 +42256,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="B239" s="9" t="s">
+      <c r="B239" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="C239" s="8" t="s">
         <v>658</v>
-      </c>
-      <c r="C239" s="8" t="s">
-        <v>659</v>
       </c>
       <c r="D239" s="8" t="s">
         <v>31</v>
@@ -41441,15 +42273,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="B240" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="B240" s="9" t="s">
+      <c r="C240" s="8" t="s">
         <v>661</v>
-      </c>
-      <c r="C240" s="8" t="s">
-        <v>662</v>
       </c>
       <c r="D240" s="8" t="s">
         <v>31</v>
@@ -41458,15 +42290,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="B241" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="B241" s="9" t="s">
+      <c r="C241" s="8" t="s">
         <v>664</v>
-      </c>
-      <c r="C241" s="8" t="s">
-        <v>665</v>
       </c>
       <c r="D241" s="8" t="s">
         <v>31</v>
@@ -41475,15 +42307,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="B242" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="B242" s="9" t="s">
+      <c r="C242" s="8" t="s">
         <v>667</v>
-      </c>
-      <c r="C242" s="8" t="s">
-        <v>668</v>
       </c>
       <c r="D242" s="8" t="s">
         <v>31</v>
@@ -41494,13 +42326,13 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="B243" s="9" t="s">
         <v>669</v>
       </c>
-      <c r="B243" s="9" t="s">
+      <c r="C243" s="8" t="s">
         <v>670</v>
-      </c>
-      <c r="C243" s="8" t="s">
-        <v>671</v>
       </c>
       <c r="D243" s="8" t="s">
         <v>31</v>
@@ -41511,13 +42343,13 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="B244" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="C244" s="8" t="s">
         <v>673</v>
-      </c>
-      <c r="C244" s="8" t="s">
-        <v>674</v>
       </c>
       <c r="D244" s="8" t="s">
         <v>31</v>
@@ -41526,15 +42358,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="B245" s="9" t="s">
         <v>675</v>
       </c>
-      <c r="B245" s="9" t="s">
+      <c r="C245" s="8" t="s">
         <v>676</v>
-      </c>
-      <c r="C245" s="8" t="s">
-        <v>677</v>
       </c>
       <c r="D245" s="8" t="s">
         <v>31</v>
@@ -41545,13 +42377,13 @@
     </row>
     <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B246" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="B246" s="9" t="s">
+      <c r="C246" s="8" t="s">
         <v>679</v>
-      </c>
-      <c r="C246" s="8" t="s">
-        <v>680</v>
       </c>
       <c r="D246" s="8" t="s">
         <v>31</v>
@@ -41560,15 +42392,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B247" s="9" t="s">
         <v>681</v>
       </c>
-      <c r="B247" s="9" t="s">
+      <c r="C247" s="8" t="s">
         <v>682</v>
-      </c>
-      <c r="C247" s="8" t="s">
-        <v>683</v>
       </c>
       <c r="D247" s="8" t="s">
         <v>31</v>
@@ -41577,15 +42409,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="B248" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="B248" s="9" t="s">
+      <c r="C248" s="8" t="s">
         <v>685</v>
-      </c>
-      <c r="C248" s="8" t="s">
-        <v>686</v>
       </c>
       <c r="D248" s="8" t="s">
         <v>31</v>
@@ -41594,15 +42426,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="B249" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="B249" s="9" t="s">
+      <c r="C249" s="8" t="s">
         <v>688</v>
-      </c>
-      <c r="C249" s="8" t="s">
-        <v>689</v>
       </c>
       <c r="D249" s="8" t="s">
         <v>31</v>
@@ -41613,13 +42445,13 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="B250" s="9" t="s">
         <v>690</v>
       </c>
-      <c r="B250" s="9" t="s">
+      <c r="C250" s="8" t="s">
         <v>691</v>
-      </c>
-      <c r="C250" s="8" t="s">
-        <v>692</v>
       </c>
       <c r="D250" s="8" t="s">
         <v>31</v>
@@ -41628,15 +42460,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="B251" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="B251" s="9" t="s">
+      <c r="C251" s="8" t="s">
         <v>694</v>
-      </c>
-      <c r="C251" s="8" t="s">
-        <v>695</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>31</v>
@@ -41645,15 +42477,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B252" s="9" t="s">
         <v>696</v>
       </c>
-      <c r="B252" s="9" t="s">
+      <c r="C252" s="8" t="s">
         <v>697</v>
-      </c>
-      <c r="C252" s="8" t="s">
-        <v>698</v>
       </c>
       <c r="D252" s="8" t="s">
         <v>31</v>
@@ -41662,15 +42494,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="B253" s="9" t="s">
         <v>699</v>
       </c>
-      <c r="B253" s="9" t="s">
+      <c r="C253" s="8" t="s">
         <v>700</v>
-      </c>
-      <c r="C253" s="8" t="s">
-        <v>701</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>31</v>
@@ -41681,13 +42513,13 @@
     </row>
     <row r="254" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="B254" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="C254" s="8" t="s">
         <v>703</v>
-      </c>
-      <c r="C254" s="8" t="s">
-        <v>704</v>
       </c>
       <c r="D254" s="8" t="s">
         <v>31</v>
@@ -41698,13 +42530,13 @@
     </row>
     <row r="255" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="B255" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="B255" s="9" t="s">
+      <c r="C255" s="8" t="s">
         <v>706</v>
-      </c>
-      <c r="C255" s="8" t="s">
-        <v>707</v>
       </c>
       <c r="D255" s="8" t="s">
         <v>31</v>
@@ -41713,15 +42545,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="B256" s="9" t="s">
         <v>708</v>
       </c>
-      <c r="B256" s="9" t="s">
+      <c r="C256" s="8" t="s">
         <v>709</v>
-      </c>
-      <c r="C256" s="8" t="s">
-        <v>710</v>
       </c>
       <c r="D256" s="8" t="s">
         <v>31</v>
@@ -41730,15 +42562,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B257" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="B257" s="9" t="s">
+      <c r="C257" s="8" t="s">
         <v>712</v>
-      </c>
-      <c r="C257" s="8" t="s">
-        <v>713</v>
       </c>
       <c r="D257" s="8" t="s">
         <v>31</v>
@@ -41749,13 +42581,13 @@
     </row>
     <row r="258" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B258" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="B258" s="9" t="s">
-        <v>712</v>
-      </c>
       <c r="C258" s="8" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D258" s="8" t="s">
         <v>31</v>
@@ -41766,13 +42598,13 @@
     </row>
     <row r="259" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="C259" s="8" t="s">
         <v>715</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>716</v>
-      </c>
-      <c r="C259" s="8" t="s">
-        <v>717</v>
       </c>
       <c r="D259" s="8" t="s">
         <v>31</v>
@@ -41783,13 +42615,13 @@
     </row>
     <row r="260" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="B260" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="B260" s="9" t="s">
+      <c r="C260" s="8" t="s">
         <v>719</v>
-      </c>
-      <c r="C260" s="8" t="s">
-        <v>720</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>31</v>
@@ -41800,13 +42632,13 @@
     </row>
     <row r="261" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="B261" s="9" t="s">
         <v>721</v>
       </c>
-      <c r="B261" s="9" t="s">
+      <c r="C261" s="8" t="s">
         <v>722</v>
-      </c>
-      <c r="C261" s="8" t="s">
-        <v>723</v>
       </c>
       <c r="D261" s="8" t="s">
         <v>31</v>
@@ -41817,13 +42649,13 @@
     </row>
     <row r="262" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="B262" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="B262" s="9" t="s">
+      <c r="C262" s="8" t="s">
         <v>725</v>
-      </c>
-      <c r="C262" s="8" t="s">
-        <v>726</v>
       </c>
       <c r="D262" s="8" t="s">
         <v>31</v>
@@ -41834,13 +42666,13 @@
     </row>
     <row r="263" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="B263" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="B263" s="9" t="s">
+      <c r="C263" s="8" t="s">
         <v>728</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>729</v>
       </c>
       <c r="D263" s="8" t="s">
         <v>31</v>
@@ -41849,15 +42681,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="B264" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="B264" s="9" t="s">
+      <c r="C264" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>732</v>
       </c>
       <c r="D264" s="8" t="s">
         <v>31</v>
@@ -41866,15 +42698,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="B265" s="9" t="s">
         <v>733</v>
       </c>
-      <c r="B265" s="9" t="s">
+      <c r="C265" s="8" t="s">
         <v>734</v>
-      </c>
-      <c r="C265" s="8" t="s">
-        <v>735</v>
       </c>
       <c r="D265" s="8" t="s">
         <v>31</v>
@@ -41883,15 +42715,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B266" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="B266" s="9" t="s">
+      <c r="C266" s="8" t="s">
         <v>737</v>
-      </c>
-      <c r="C266" s="8" t="s">
-        <v>738</v>
       </c>
       <c r="D266" s="8" t="s">
         <v>31</v>
@@ -41900,15 +42732,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B267" s="9" t="s">
         <v>739</v>
       </c>
-      <c r="B267" s="9" t="s">
+      <c r="C267" s="8" t="s">
         <v>740</v>
-      </c>
-      <c r="C267" s="8" t="s">
-        <v>741</v>
       </c>
       <c r="D267" s="8" t="s">
         <v>31</v>
@@ -41917,15 +42749,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="B268" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="B268" s="9" t="s">
+      <c r="C268" s="8" t="s">
         <v>743</v>
-      </c>
-      <c r="C268" s="8" t="s">
-        <v>744</v>
       </c>
       <c r="D268" s="8" t="s">
         <v>31</v>
@@ -41936,13 +42768,13 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="B269" s="9" t="s">
         <v>745</v>
       </c>
-      <c r="B269" s="9" t="s">
+      <c r="C269" s="8" t="s">
         <v>746</v>
-      </c>
-      <c r="C269" s="8" t="s">
-        <v>747</v>
       </c>
       <c r="D269" s="8" t="s">
         <v>31</v>
@@ -41951,15 +42783,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="B270" s="9" t="s">
         <v>748</v>
       </c>
-      <c r="B270" s="9" t="s">
+      <c r="C270" s="8" t="s">
         <v>749</v>
-      </c>
-      <c r="C270" s="8" t="s">
-        <v>750</v>
       </c>
       <c r="D270" s="8" t="s">
         <v>31</v>
@@ -41968,15 +42800,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="B271" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="B271" s="9" t="s">
+      <c r="C271" s="8" t="s">
         <v>752</v>
-      </c>
-      <c r="C271" s="8" t="s">
-        <v>753</v>
       </c>
       <c r="D271" s="8" t="s">
         <v>31</v>
@@ -41987,13 +42819,13 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="B272" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="B272" s="9" t="s">
+      <c r="C272" s="8" t="s">
         <v>755</v>
-      </c>
-      <c r="C272" s="8" t="s">
-        <v>756</v>
       </c>
       <c r="D272" s="8" t="s">
         <v>31</v>
@@ -42004,13 +42836,13 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="B273" s="9" t="s">
         <v>757</v>
       </c>
-      <c r="B273" s="9" t="s">
+      <c r="C273" s="8" t="s">
         <v>758</v>
-      </c>
-      <c r="C273" s="8" t="s">
-        <v>759</v>
       </c>
       <c r="D273" s="8" t="s">
         <v>31</v>
@@ -42021,13 +42853,13 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="B274" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="B274" s="9" t="s">
+      <c r="C274" s="8" t="s">
         <v>761</v>
-      </c>
-      <c r="C274" s="8" t="s">
-        <v>762</v>
       </c>
       <c r="D274" s="8" t="s">
         <v>31</v>
@@ -42038,13 +42870,13 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B275" s="9" t="s">
         <v>763</v>
       </c>
-      <c r="B275" s="9" t="s">
+      <c r="C275" s="8" t="s">
         <v>764</v>
-      </c>
-      <c r="C275" s="8" t="s">
-        <v>765</v>
       </c>
       <c r="D275" s="8" t="s">
         <v>31</v>
@@ -42055,13 +42887,13 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="B276" s="9" t="s">
         <v>766</v>
       </c>
-      <c r="B276" s="9" t="s">
+      <c r="C276" s="8" t="s">
         <v>767</v>
-      </c>
-      <c r="C276" s="8" t="s">
-        <v>768</v>
       </c>
       <c r="D276" s="8" t="s">
         <v>31</v>
@@ -42072,13 +42904,13 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="B277" s="9" t="s">
         <v>769</v>
       </c>
-      <c r="B277" s="9" t="s">
+      <c r="C277" s="8" t="s">
         <v>770</v>
-      </c>
-      <c r="C277" s="8" t="s">
-        <v>771</v>
       </c>
       <c r="D277" s="8" t="s">
         <v>31</v>
@@ -42088,31 +42920,31 @@
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="11" t="s">
+      <c r="A278" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="B278" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="B278" s="10" t="s">
+      <c r="C278" s="8" t="s">
         <v>773</v>
       </c>
-      <c r="C278" s="10" t="s">
-        <v>774</v>
-      </c>
-      <c r="D278" s="10" t="s">
+      <c r="D278" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E278" s="10" t="s">
+      <c r="E278" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="11" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B279" s="10" t="s">
         <v>775</v>
       </c>
       <c r="C279" s="10" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>31</v>
@@ -42123,13 +42955,13 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="11" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B280" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="C280" s="10" t="s">
         <v>776</v>
-      </c>
-      <c r="C280" s="10" t="s">
-        <v>774</v>
       </c>
       <c r="D280" s="10" t="s">
         <v>31</v>
@@ -42138,32 +42970,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="9" t="s">
-        <v>777</v>
-      </c>
-      <c r="B281" s="9" t="s">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="B281" s="10" t="s">
+        <v>778</v>
+      </c>
+      <c r="C281" s="10" t="s">
+        <v>776</v>
+      </c>
+      <c r="D281" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E281" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="B282" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C281" s="8" t="s">
+      <c r="C282" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="D281" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E281" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="282" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="9" t="s">
-        <v>777</v>
-      </c>
-      <c r="B282" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="C282" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="D282" s="8" t="s">
         <v>31</v>
@@ -42172,15 +43004,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="9" t="s">
         <v>779</v>
       </c>
       <c r="B283" s="9" t="s">
-        <v>72</v>
+        <v>780</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>192</v>
+        <v>67</v>
       </c>
       <c r="D283" s="8" t="s">
         <v>31</v>
@@ -42189,15 +43021,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="9" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B284" s="9" t="s">
-        <v>780</v>
+        <v>72</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>781</v>
+        <v>192</v>
       </c>
       <c r="D284" s="8" t="s">
         <v>31</v>
@@ -42206,15 +43038,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="B285" s="9" t="s">
         <v>782</v>
       </c>
-      <c r="B285" s="9" t="s">
+      <c r="C285" s="8" t="s">
         <v>783</v>
-      </c>
-      <c r="C285" s="8" t="s">
-        <v>784</v>
       </c>
       <c r="D285" s="8" t="s">
         <v>31</v>
@@ -42225,13 +43057,13 @@
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="B286" s="9" t="s">
         <v>785</v>
       </c>
-      <c r="B286" s="9" t="s">
+      <c r="C286" s="8" t="s">
         <v>786</v>
-      </c>
-      <c r="C286" s="8" t="s">
-        <v>787</v>
       </c>
       <c r="D286" s="8" t="s">
         <v>31</v>
@@ -42242,13 +43074,13 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="B287" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="B287" s="9" t="s">
+      <c r="C287" s="8" t="s">
         <v>789</v>
-      </c>
-      <c r="C287" s="8" t="s">
-        <v>790</v>
       </c>
       <c r="D287" s="8" t="s">
         <v>31</v>
@@ -42258,14 +43090,14 @@
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="8" t="s">
+      <c r="A288" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="B288" s="9" t="s">
         <v>791</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="C288" s="8" t="s">
         <v>792</v>
-      </c>
-      <c r="C288" s="8" t="s">
-        <v>793</v>
       </c>
       <c r="D288" s="8" t="s">
         <v>31</v>
@@ -42274,32 +43106,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="10" t="s">
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="B289" s="9" t="s">
         <v>794</v>
       </c>
-      <c r="B289" s="11" t="s">
+      <c r="C289" s="8" t="s">
         <v>795</v>
       </c>
-      <c r="C289" s="10" t="s">
-        <v>796</v>
-      </c>
-      <c r="D289" s="10" t="s">
+      <c r="D289" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E289" s="10" t="s">
+      <c r="E289" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="B290" s="11" t="s">
         <v>797</v>
       </c>
-      <c r="B290" s="11" t="s">
+      <c r="C290" s="10" t="s">
         <v>798</v>
-      </c>
-      <c r="C290" s="10" t="s">
-        <v>796</v>
       </c>
       <c r="D290" s="10" t="s">
         <v>31</v>
@@ -42316,7 +43148,7 @@
         <v>800</v>
       </c>
       <c r="C291" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D291" s="10" t="s">
         <v>31</v>
@@ -42333,7 +43165,7 @@
         <v>802</v>
       </c>
       <c r="C292" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D292" s="10" t="s">
         <v>31</v>
@@ -42350,7 +43182,7 @@
         <v>804</v>
       </c>
       <c r="C293" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D293" s="10" t="s">
         <v>31</v>
@@ -42367,7 +43199,7 @@
         <v>806</v>
       </c>
       <c r="C294" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D294" s="10" t="s">
         <v>31</v>
@@ -42384,7 +43216,7 @@
         <v>808</v>
       </c>
       <c r="C295" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D295" s="10" t="s">
         <v>31</v>
@@ -42401,7 +43233,7 @@
         <v>810</v>
       </c>
       <c r="C296" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D296" s="10" t="s">
         <v>31</v>
@@ -42418,7 +43250,7 @@
         <v>812</v>
       </c>
       <c r="C297" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D297" s="10" t="s">
         <v>31</v>
@@ -42435,7 +43267,7 @@
         <v>814</v>
       </c>
       <c r="C298" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D298" s="10" t="s">
         <v>31</v>
@@ -42452,7 +43284,7 @@
         <v>816</v>
       </c>
       <c r="C299" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D299" s="10" t="s">
         <v>31</v>
@@ -42462,14 +43294,14 @@
       </c>
     </row>
     <row r="300" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="11" t="s">
+      <c r="A300" s="10" t="s">
         <v>817</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>818</v>
       </c>
       <c r="C300" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D300" s="10" t="s">
         <v>31</v>
@@ -42486,7 +43318,7 @@
         <v>820</v>
       </c>
       <c r="C301" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D301" s="10" t="s">
         <v>31</v>
@@ -42496,14 +43328,14 @@
       </c>
     </row>
     <row r="302" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="10" t="s">
+      <c r="A302" s="11" t="s">
         <v>821</v>
       </c>
       <c r="B302" s="11" t="s">
         <v>822</v>
       </c>
       <c r="C302" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D302" s="10" t="s">
         <v>31</v>
@@ -42520,7 +43352,7 @@
         <v>824</v>
       </c>
       <c r="C303" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D303" s="10" t="s">
         <v>31</v>
@@ -42537,7 +43369,7 @@
         <v>826</v>
       </c>
       <c r="C304" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D304" s="10" t="s">
         <v>31</v>
@@ -42554,7 +43386,7 @@
         <v>828</v>
       </c>
       <c r="C305" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D305" s="10" t="s">
         <v>31</v>
@@ -42571,7 +43403,7 @@
         <v>830</v>
       </c>
       <c r="C306" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D306" s="10" t="s">
         <v>31</v>
@@ -42581,14 +43413,14 @@
       </c>
     </row>
     <row r="307" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="11" t="s">
+      <c r="A307" s="10" t="s">
         <v>831</v>
       </c>
       <c r="B307" s="11" t="s">
         <v>832</v>
       </c>
       <c r="C307" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D307" s="10" t="s">
         <v>31</v>
@@ -42598,14 +43430,14 @@
       </c>
     </row>
     <row r="308" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="11" t="s">
+      <c r="A308" s="10" t="s">
         <v>833</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>834</v>
       </c>
       <c r="C308" s="10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D308" s="10" t="s">
         <v>31</v>
@@ -42614,8 +43446,76 @@
         <v>32</v>
       </c>
     </row>
+    <row r="309" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A309" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="B309" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="C309" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="D309" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E309" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A310" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="B310" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="C310" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="D310" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E310" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="B311" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="C311" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="D311" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E311" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="B312" s="11" t="s">
+        <v>842</v>
+      </c>
+      <c r="C312" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="D312" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E312" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E308"/>
+  <autoFilter ref="A1:E312"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -42644,7 +43544,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>23</v>
@@ -42689,66 +43589,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -42769,7 +43669,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -42782,27 +43682,27 @@
         <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42810,13 +43710,13 @@
         <v>38</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42824,13 +43724,13 @@
         <v>137</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42838,13 +43738,13 @@
         <v>277</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42852,27 +43752,27 @@
         <v>283</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42880,27 +43780,27 @@
         <v>114</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>72</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42908,13 +43808,13 @@
         <v>130</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42922,13 +43822,13 @@
         <v>149</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42936,13 +43836,13 @@
         <v>368</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42950,13 +43850,13 @@
         <v>382</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42964,13 +43864,13 @@
         <v>385</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42978,13 +43878,13 @@
         <v>397</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42992,185 +43892,199 @@
         <v>406</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>940</v>
+        <v>948</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>949</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>943</v>
+        <v>103</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>944</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>945</v>
+        <v>952</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>957</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D28"/>
+  <autoFilter ref="A1:D29"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">专项检查!$A$1:$B$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$29</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$30</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$312</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">问题汇总!$A$1:$F$3</definedName>
   </definedNames>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="963">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="967">
   <si>
     <r>
       <rPr>
@@ -8680,7 +8680,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">117 … two independent readers … two elements documented in more than seven examinations … Three examinations … 5 of 58</t>
+    <t xml:space="preserve">117 … two independent readers … the two most often documented elements in panel A … Three examinations … 5 of 58</t>
   </si>
   <si>
     <r>
@@ -11224,7 +11224,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">n (%) of 117 | 2012–2018 (n=38) | 2019–2026 (n=79)</t>
+    <t xml:space="preserve">n (%) of 117 | 2012–2018, n (of 38) | 2019–2026, n (of 79)</t>
   </si>
   <si>
     <r>
@@ -31269,7 +31269,7 @@
     <t xml:space="preserve">Title Page · Word count</t>
   </si>
   <si>
-    <t xml:space="preserve">2,995 … Abstract: 249 words</t>
+    <t xml:space="preserve">2,996 … Abstract: 249 words</t>
   </si>
   <si>
     <r>
@@ -31304,7 +31304,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2995</t>
+      <t xml:space="preserve">2996</t>
     </r>
     <r>
       <rPr>
@@ -31427,7 +31427,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Word count: 2,995 … Tables: 4; Figures: 3; Supplements 1–4</t>
+    <t xml:space="preserve">Word count: 2,996 … Tables: 4; Figures: 3; Supplements 1–4</t>
   </si>
   <si>
     <r>
@@ -31445,7 +31445,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2995</t>
+      <t xml:space="preserve">2996</t>
     </r>
   </si>
   <si>
@@ -32580,7 +32580,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">two elements</t>
+      <t xml:space="preserve">two most</t>
     </r>
     <r>
       <rPr>
@@ -37464,6 +37464,397 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">一致</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结果 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">队列 第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段；结果 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">亚组 第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段；补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 S2.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S2.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；图 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">图注；表 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列标题（通读后措辞）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">… detection was higher in that position (… vs … for the UGI series)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">in whom the diagnosis remained uncertain / was assembled by diagnostic uncertainty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">two elements documented in more than seven examinations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2012–2018 (n=38)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">… UGI detection was higher when it came last (… vs … when it did not)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">presumably selected / assembled by diagnostic uncertainty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">the two most often documented elements in panel A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2012–2018, n (of 38)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">补明对比对象；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">诊断不确定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">是对临床医生考虑的推测，数据未记录检查指征，加 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">presumably</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；图 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">选取规则改为图 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中记录最多的两项；表 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">时期列只有计数，列标题补 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">n</t>
     </r>
   </si>
   <si>
@@ -43879,7 +44270,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -44279,22 +44670,36 @@
         <v>958</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
         <v>959</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>960</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="9" t="s">
         <v>961</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>962</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>964</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>966</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D29"/>
+  <autoFilter ref="A1:D30"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">专项检查!$A$1:$B$8</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$31</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$312</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">问题汇总!$A$1:$F$1</definedName>
   </definedNames>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="966">
   <si>
     <r>
       <rPr>
@@ -31328,7 +31328,7 @@
     <t xml:space="preserve">Title Page · Word count</t>
   </si>
   <si>
-    <t xml:space="preserve">2,996 … Abstract: 249 words</t>
+    <t xml:space="preserve">2,998 … Abstract: 249 words</t>
   </si>
   <si>
     <r>
@@ -31363,7 +31363,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2996</t>
+      <t xml:space="preserve">2998</t>
     </r>
     <r>
       <rPr>
@@ -31486,7 +31486,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Word count: 2,996 … Tables: 4; Figures: 3; Supplements 1–4</t>
+    <t xml:space="preserve">Word count: 2,998 … Tables: 4; Figures: 3; Supplements 1–4</t>
   </si>
   <si>
     <r>
@@ -31504,7 +31504,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2996</t>
+      <t xml:space="preserve">2998</t>
     </r>
   </si>
   <si>
@@ -37911,6 +37911,109 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方法 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内容编码；表 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">注；补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 · K3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（阅读者与报告）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">both authors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both authors who had reported none of the examinations</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用户 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">确认两位超声阅读者均未出具被审计的超声报告；为腾字数删去引言末段 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"that other departments can apply"</t>
     </r>
   </si>
   <si>
@@ -44264,7 +44367,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -44678,22 +44781,36 @@
         <v>957</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
         <v>958</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>959</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="9" t="s">
         <v>960</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>961</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>963</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>965</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D30"/>
+  <autoFilter ref="A1:D31"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">专项检查!$A$1:$B$8</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$34</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$355</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$356</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">问题汇总!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="1085">
   <si>
     <r>
       <rPr>
@@ -8398,6 +8398,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">revisions of the 2020 ACR guidance [19]</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -34963,7 +34966,7 @@
     <t xml:space="preserve">Title Page · Word count</t>
   </si>
   <si>
-    <t xml:space="preserve">2,998 … Abstract: 248 words</t>
+    <t xml:space="preserve">2,999 … Abstract: 248 words</t>
   </si>
   <si>
     <r>
@@ -34998,7 +35001,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2998</t>
+      <t xml:space="preserve">2999</t>
     </r>
     <r>
       <rPr>
@@ -35121,7 +35124,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Word count: 2,998 … Tables: 4; Figures: 3; Supplements 1–4</t>
+    <t xml:space="preserve">Word count: 2,999 … Tables: 4; Figures: 3; Supplements 1–4</t>
   </si>
   <si>
     <r>
@@ -35139,7 +35142,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2998</t>
+      <t xml:space="preserve">2999</t>
     </r>
   </si>
   <si>
@@ -44836,7 +44839,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(核对表!B2:B2000)</f>
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44845,7 +44848,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(核对表!C2:C2000,"【一致】*")</f>
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44909,7 +44912,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E355"/>
+  <dimension ref="A1:E356"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -46261,15 +46264,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="114.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>208</v>
-      </c>
       <c r="C80" s="8" t="s">
-        <v>209</v>
+        <v>67</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>31</v>
@@ -46278,15 +46281,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="9" t="s">
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>212</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>31</v>
@@ -46297,13 +46300,13 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C82" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>215</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>31</v>
@@ -46313,14 +46316,14 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>218</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>31</v>
@@ -46330,48 +46333,48 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="B84" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C85" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="D85" s="8" t="s">
+      <c r="D85" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E85" s="8" t="s">
+      <c r="E85" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>227</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>31</v>
@@ -46381,48 +46384,48 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="D87" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="B88" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="C88" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E88" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="B88" s="9" t="s">
+    <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="B89" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D88" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8" t="s">
+      <c r="C89" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>236</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>31</v>
@@ -46431,15 +46434,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>239</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>31</v>
@@ -46450,13 +46453,13 @@
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C91" s="8" t="s">
         <v>240</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>242</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>31</v>
@@ -46467,13 +46470,13 @@
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>245</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>31</v>
@@ -46484,13 +46487,13 @@
     </row>
     <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>248</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>31</v>
@@ -46501,13 +46504,13 @@
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C94" s="8" t="s">
         <v>249</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>251</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>31</v>
@@ -46518,13 +46521,13 @@
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>252</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>254</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>31</v>
@@ -46535,13 +46538,13 @@
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>257</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>31</v>
@@ -46552,13 +46555,13 @@
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C97" s="8" t="s">
         <v>258</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>260</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>31</v>
@@ -46569,13 +46572,13 @@
     </row>
     <row r="98" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C98" s="8" t="s">
         <v>261</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>263</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>31</v>
@@ -46586,13 +46589,13 @@
     </row>
     <row r="99" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C99" s="8" t="s">
         <v>264</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>266</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>31</v>
@@ -46603,13 +46606,13 @@
     </row>
     <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="B100" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>269</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>31</v>
@@ -46620,13 +46623,13 @@
     </row>
     <row r="101" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>272</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>31</v>
@@ -46635,15 +46638,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C102" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="B102" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>275</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>31</v>
@@ -46652,15 +46655,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C103" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="B103" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>278</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>31</v>
@@ -46671,13 +46674,13 @@
     </row>
     <row r="104" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C104" s="8" t="s">
         <v>279</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>281</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>31</v>
@@ -46688,13 +46691,13 @@
     </row>
     <row r="105" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C105" s="8" t="s">
         <v>282</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>284</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>31</v>
@@ -46703,15 +46706,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C106" s="8" t="s">
         <v>285</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>287</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>31</v>
@@ -46722,13 +46725,13 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>31</v>
@@ -46739,13 +46742,13 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C108" s="8" t="s">
         <v>291</v>
-      </c>
-      <c r="B108" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>293</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>31</v>
@@ -46754,15 +46757,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>294</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>296</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>31</v>
@@ -46773,13 +46776,13 @@
     </row>
     <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>299</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>31</v>
@@ -46790,13 +46793,13 @@
     </row>
     <row r="111" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>302</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>31</v>
@@ -46807,13 +46810,13 @@
     </row>
     <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" s="8" t="s">
         <v>303</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>305</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>31</v>
@@ -46824,13 +46827,13 @@
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C113" s="8" t="s">
         <v>306</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>308</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>31</v>
@@ -46841,13 +46844,13 @@
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="C114" s="8" t="s">
         <v>309</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>311</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>31</v>
@@ -46858,13 +46861,13 @@
     </row>
     <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C115" s="8" t="s">
         <v>312</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>314</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>31</v>
@@ -46875,13 +46878,13 @@
     </row>
     <row r="116" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="C116" s="8" t="s">
         <v>315</v>
-      </c>
-      <c r="B116" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>31</v>
@@ -46890,15 +46893,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C117" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="B117" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>320</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>31</v>
@@ -46907,15 +46910,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C118" s="8" t="s">
         <v>321</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>31</v>
@@ -46924,15 +46927,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C119" s="8" t="s">
         <v>324</v>
-      </c>
-      <c r="B119" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>326</v>
       </c>
       <c r="D119" s="8" t="s">
         <v>31</v>
@@ -46943,13 +46946,13 @@
     </row>
     <row r="120" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C120" s="8" t="s">
         <v>327</v>
-      </c>
-      <c r="B120" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>329</v>
       </c>
       <c r="D120" s="8" t="s">
         <v>31</v>
@@ -46960,13 +46963,13 @@
     </row>
     <row r="121" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C121" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>332</v>
       </c>
       <c r="D121" s="8" t="s">
         <v>31</v>
@@ -46975,15 +46978,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C122" s="8" t="s">
         <v>333</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>335</v>
       </c>
       <c r="D122" s="8" t="s">
         <v>31</v>
@@ -46994,13 +46997,13 @@
     </row>
     <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C123" s="8" t="s">
         <v>336</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>338</v>
       </c>
       <c r="D123" s="8" t="s">
         <v>31</v>
@@ -47009,15 +47012,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C124" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="B124" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>341</v>
       </c>
       <c r="D124" s="8" t="s">
         <v>31</v>
@@ -47026,15 +47029,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C125" s="8" t="s">
         <v>342</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>344</v>
       </c>
       <c r="D125" s="8" t="s">
         <v>31</v>
@@ -47043,15 +47046,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C126" s="8" t="s">
         <v>345</v>
-      </c>
-      <c r="B126" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>347</v>
       </c>
       <c r="D126" s="8" t="s">
         <v>31</v>
@@ -47062,13 +47065,13 @@
     </row>
     <row r="127" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C127" s="8" t="s">
         <v>348</v>
-      </c>
-      <c r="B127" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>350</v>
       </c>
       <c r="D127" s="8" t="s">
         <v>31</v>
@@ -47079,47 +47082,47 @@
     </row>
     <row r="128" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C128" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="B128" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>353</v>
-      </c>
       <c r="D128" s="8" t="s">
-        <v>354</v>
+        <v>31</v>
       </c>
       <c r="E128" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D129" s="8" t="s">
         <v>355</v>
-      </c>
-      <c r="B129" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="E129" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="41" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C130" s="8" t="s">
         <v>358</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>360</v>
       </c>
       <c r="D130" s="8" t="s">
         <v>31</v>
@@ -47128,15 +47131,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="41" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C131" s="8" t="s">
         <v>361</v>
-      </c>
-      <c r="B131" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>363</v>
       </c>
       <c r="D131" s="8" t="s">
         <v>31</v>
@@ -47145,66 +47148,66 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="10" t="s">
+    <row r="132" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="C132" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="B132" s="11" t="s">
+      <c r="D132" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="B133" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="C133" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D133" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E132" s="10" t="s">
+      <c r="E133" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="B133" s="9" t="s">
+    <row r="134" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="B134" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="D133" s="8" t="s">
+      <c r="C134" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D134" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E133" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="B134" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E134" s="10" t="s">
+      <c r="E134" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="C135" s="10" t="s">
         <v>373</v>
-      </c>
-      <c r="B135" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>374</v>
       </c>
       <c r="D135" s="10" t="s">
         <v>31</v>
@@ -47213,32 +47216,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="8" t="s">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B136" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="D136" s="8" t="s">
+      <c r="D136" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E136" s="8" t="s">
+      <c r="E136" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>378</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>380</v>
       </c>
       <c r="D137" s="8" t="s">
         <v>31</v>
@@ -47247,15 +47250,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="C138" s="8" t="s">
         <v>381</v>
-      </c>
-      <c r="B138" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>383</v>
       </c>
       <c r="D138" s="8" t="s">
         <v>31</v>
@@ -47264,15 +47267,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="C139" s="8" t="s">
         <v>384</v>
-      </c>
-      <c r="B139" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>386</v>
       </c>
       <c r="D139" s="8" t="s">
         <v>31</v>
@@ -47281,15 +47284,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B140" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="C140" s="8" t="s">
         <v>387</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>388</v>
       </c>
       <c r="D140" s="8" t="s">
         <v>31</v>
@@ -47298,15 +47301,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B141" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C141" s="8" t="s">
         <v>389</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>390</v>
       </c>
       <c r="D141" s="8" t="s">
         <v>31</v>
@@ -47315,15 +47318,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>391</v>
-      </c>
-      <c r="B142" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>393</v>
       </c>
       <c r="D142" s="8" t="s">
         <v>31</v>
@@ -47332,49 +47335,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="10" t="s">
+    <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C143" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="D143" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="C143" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D143" s="10" t="s">
+      <c r="B144" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D144" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E143" s="10" t="s">
+      <c r="E144" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="B144" s="9" t="s">
+    <row r="145" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="B145" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="D144" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="B145" s="9" t="s">
+      <c r="C145" s="8" t="s">
         <v>399</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>400</v>
       </c>
       <c r="D145" s="8" t="s">
         <v>31</v>
@@ -47383,15 +47386,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B146" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="C146" s="8" t="s">
         <v>401</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>402</v>
       </c>
       <c r="D146" s="8" t="s">
         <v>31</v>
@@ -47400,15 +47403,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B147" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="C147" s="8" t="s">
         <v>403</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>404</v>
       </c>
       <c r="D147" s="8" t="s">
         <v>31</v>
@@ -47417,15 +47420,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>405</v>
-      </c>
-      <c r="B148" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>407</v>
       </c>
       <c r="D148" s="8" t="s">
         <v>31</v>
@@ -47434,83 +47437,83 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="10" t="s">
+    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="C149" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="D149" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D149" s="10" t="s">
+      <c r="B150" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D150" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E149" s="10" t="s">
+      <c r="E150" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="B150" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="C150" s="8" t="s">
+    <row r="151" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="B151" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="D150" s="8" t="s">
+      <c r="C151" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="D151" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E151" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="B151" s="11" t="s">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="B152" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="D151" s="10" t="s">
+      <c r="C152" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="D152" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E151" s="10" t="s">
+      <c r="E152" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="B152" s="9" t="s">
+    <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="B153" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="D152" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="B153" s="9" t="s">
+      <c r="C153" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="D153" s="8" t="s">
         <v>31</v>
@@ -47519,15 +47522,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="C154" s="8" t="s">
         <v>420</v>
-      </c>
-      <c r="B154" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>422</v>
       </c>
       <c r="D154" s="8" t="s">
         <v>31</v>
@@ -47536,15 +47539,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="C155" s="8" t="s">
         <v>423</v>
-      </c>
-      <c r="B155" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>425</v>
       </c>
       <c r="D155" s="8" t="s">
         <v>31</v>
@@ -47553,15 +47556,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="B156" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>400</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>31</v>
@@ -47572,13 +47575,13 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="B157" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="B157" s="9" t="s">
-        <v>429</v>
-      </c>
       <c r="C157" s="8" t="s">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="D157" s="8" t="s">
         <v>31</v>
@@ -47587,15 +47590,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B158" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C158" s="8" t="s">
         <v>431</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>432</v>
       </c>
       <c r="D158" s="8" t="s">
         <v>31</v>
@@ -47604,15 +47607,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C159" s="8" t="s">
         <v>433</v>
-      </c>
-      <c r="B159" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>435</v>
       </c>
       <c r="D159" s="8" t="s">
         <v>31</v>
@@ -47623,13 +47626,13 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B160" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C160" s="8" t="s">
         <v>436</v>
-      </c>
-      <c r="C160" s="8" t="s">
-        <v>437</v>
       </c>
       <c r="D160" s="8" t="s">
         <v>31</v>
@@ -47640,13 +47643,13 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C161" s="8" t="s">
         <v>438</v>
-      </c>
-      <c r="B161" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>440</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>31</v>
@@ -47657,13 +47660,13 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="C162" s="8" t="s">
         <v>441</v>
-      </c>
-      <c r="B162" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>443</v>
       </c>
       <c r="D162" s="8" t="s">
         <v>31</v>
@@ -47674,13 +47677,13 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C163" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="B163" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>446</v>
       </c>
       <c r="D163" s="8" t="s">
         <v>31</v>
@@ -47689,15 +47692,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="C164" s="8" t="s">
         <v>447</v>
-      </c>
-      <c r="B164" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>449</v>
       </c>
       <c r="D164" s="8" t="s">
         <v>31</v>
@@ -47706,15 +47709,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="C165" s="8" t="s">
         <v>450</v>
-      </c>
-      <c r="B165" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>452</v>
       </c>
       <c r="D165" s="8" t="s">
         <v>31</v>
@@ -47725,13 +47728,13 @@
     </row>
     <row r="166" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="C166" s="8" t="s">
         <v>453</v>
-      </c>
-      <c r="B166" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>455</v>
       </c>
       <c r="D166" s="8" t="s">
         <v>31</v>
@@ -47742,13 +47745,13 @@
     </row>
     <row r="167" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="C167" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="B167" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>458</v>
       </c>
       <c r="D167" s="8" t="s">
         <v>31</v>
@@ -47757,15 +47760,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="8" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B168" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="C168" s="8" t="s">
         <v>459</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>460</v>
       </c>
       <c r="D168" s="8" t="s">
         <v>31</v>
@@ -47774,15 +47777,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C169" s="8" t="s">
         <v>461</v>
-      </c>
-      <c r="B169" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>463</v>
       </c>
       <c r="D169" s="8" t="s">
         <v>31</v>
@@ -47793,13 +47796,13 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="8" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B170" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="C170" s="8" t="s">
         <v>464</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>465</v>
       </c>
       <c r="D170" s="8" t="s">
         <v>31</v>
@@ -47808,15 +47811,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="C171" s="8" t="s">
         <v>466</v>
-      </c>
-      <c r="B171" s="9" t="s">
-        <v>467</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>468</v>
       </c>
       <c r="D171" s="8" t="s">
         <v>31</v>
@@ -47825,32 +47828,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="B172" s="11" t="s">
+    <row r="172" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C172" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="C172" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D172" s="10" t="s">
+      <c r="D172" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E172" s="10" t="s">
+      <c r="E172" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="C173" s="10" t="s">
         <v>471</v>
-      </c>
-      <c r="B173" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="C173" s="10" t="s">
-        <v>366</v>
       </c>
       <c r="D173" s="10" t="s">
         <v>31</v>
@@ -47859,66 +47862,66 @@
         <v>32</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="8" t="s">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B174" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="B174" s="9" t="s">
+      <c r="C174" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D174" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E174" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="C174" s="8" t="s">
+      <c r="B175" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="D174" s="8" t="s">
+      <c r="C175" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="D175" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E174" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="175" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="B175" s="11" t="s">
-        <v>477</v>
-      </c>
-      <c r="C175" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="D175" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E175" s="10" t="s">
+      <c r="E175" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="B176" s="9" t="s">
+      <c r="A176" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="C176" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="C176" s="8" t="s">
+      <c r="D176" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B177" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="D176" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="8" t="s">
+      <c r="C177" s="8" t="s">
         <v>481</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>482</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>483</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>31</v>
@@ -47927,15 +47930,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C178" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="B178" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>486</v>
       </c>
       <c r="D178" s="8" t="s">
         <v>31</v>
@@ -47944,49 +47947,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="10" t="s">
+    <row r="179" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="C179" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="B179" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C179" s="10" t="s">
+      <c r="D179" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B180" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="D179" s="10" t="s">
+      <c r="C180" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="D180" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E179" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="180" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="B180" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E180" s="8" t="s">
+      <c r="E180" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C181" s="8" t="s">
         <v>491</v>
-      </c>
-      <c r="B181" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="C181" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="D181" s="8" t="s">
         <v>31</v>
@@ -47997,13 +48000,13 @@
     </row>
     <row r="182" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C182" s="8" t="s">
         <v>494</v>
-      </c>
-      <c r="B182" s="9" t="s">
-        <v>489</v>
-      </c>
-      <c r="C182" s="8" t="s">
-        <v>495</v>
       </c>
       <c r="D182" s="8" t="s">
         <v>31</v>
@@ -48012,15 +48015,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="C183" s="8" t="s">
         <v>496</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="C183" s="8" t="s">
-        <v>498</v>
       </c>
       <c r="D183" s="8" t="s">
         <v>31</v>
@@ -48031,13 +48034,13 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="C184" s="8" t="s">
         <v>499</v>
-      </c>
-      <c r="B184" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="C184" s="8" t="s">
-        <v>501</v>
       </c>
       <c r="D184" s="8" t="s">
         <v>31</v>
@@ -48048,13 +48051,13 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="C185" s="8" t="s">
         <v>502</v>
-      </c>
-      <c r="B185" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="C185" s="8" t="s">
-        <v>503</v>
       </c>
       <c r="D185" s="8" t="s">
         <v>31</v>
@@ -48063,15 +48066,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C186" s="8" t="s">
         <v>504</v>
-      </c>
-      <c r="B186" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="C186" s="8" t="s">
-        <v>506</v>
       </c>
       <c r="D186" s="8" t="s">
         <v>31</v>
@@ -48080,15 +48083,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="C187" s="8" t="s">
         <v>507</v>
-      </c>
-      <c r="B187" s="9" t="s">
-        <v>508</v>
-      </c>
-      <c r="C187" s="8" t="s">
-        <v>509</v>
       </c>
       <c r="D187" s="8" t="s">
         <v>31</v>
@@ -48099,13 +48102,13 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="C188" s="8" t="s">
         <v>510</v>
-      </c>
-      <c r="B188" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="C188" s="8" t="s">
-        <v>512</v>
       </c>
       <c r="D188" s="8" t="s">
         <v>31</v>
@@ -48114,15 +48117,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="C189" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="B189" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>515</v>
       </c>
       <c r="D189" s="8" t="s">
         <v>31</v>
@@ -48133,13 +48136,13 @@
     </row>
     <row r="190" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="C190" s="8" t="s">
         <v>516</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="C190" s="8" t="s">
-        <v>503</v>
       </c>
       <c r="D190" s="8" t="s">
         <v>31</v>
@@ -48148,15 +48151,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="8" t="s">
         <v>517</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="D191" s="8" t="s">
         <v>31</v>
@@ -48166,48 +48169,48 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="10" t="s">
+      <c r="A192" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="C192" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="D192" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="C192" s="10" t="s">
+      <c r="B193" s="10" t="s">
         <v>522</v>
       </c>
-      <c r="D192" s="10" t="s">
+      <c r="C193" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="D193" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E192" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="193" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="B193" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="C193" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="D193" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E193" s="8" t="s">
+      <c r="E193" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="C194" s="8" t="s">
         <v>526</v>
-      </c>
-      <c r="B194" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C194" s="8" t="s">
-        <v>528</v>
       </c>
       <c r="D194" s="8" t="s">
         <v>31</v>
@@ -48218,13 +48221,13 @@
     </row>
     <row r="195" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C195" s="8" t="s">
         <v>529</v>
-      </c>
-      <c r="B195" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="C195" s="8" t="s">
-        <v>531</v>
       </c>
       <c r="D195" s="8" t="s">
         <v>31</v>
@@ -48235,13 +48238,13 @@
     </row>
     <row r="196" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="C196" s="8" t="s">
         <v>532</v>
-      </c>
-      <c r="B196" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>534</v>
       </c>
       <c r="D196" s="8" t="s">
         <v>31</v>
@@ -48252,13 +48255,13 @@
     </row>
     <row r="197" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="C197" s="8" t="s">
         <v>535</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C197" s="8" t="s">
-        <v>528</v>
       </c>
       <c r="D197" s="8" t="s">
         <v>31</v>
@@ -48272,10 +48275,10 @@
         <v>536</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="D198" s="8" t="s">
         <v>31</v>
@@ -48286,13 +48289,13 @@
     </row>
     <row r="199" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="C199" s="8" t="s">
         <v>539</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="C199" s="8" t="s">
-        <v>541</v>
       </c>
       <c r="D199" s="8" t="s">
         <v>31</v>
@@ -48303,13 +48306,13 @@
     </row>
     <row r="200" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="C200" s="8" t="s">
         <v>542</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="C200" s="8" t="s">
-        <v>528</v>
       </c>
       <c r="D200" s="8" t="s">
         <v>31</v>
@@ -48323,10 +48326,10 @@
         <v>543</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="D201" s="8" t="s">
         <v>31</v>
@@ -48337,13 +48340,13 @@
     </row>
     <row r="202" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C202" s="8" t="s">
         <v>546</v>
-      </c>
-      <c r="B202" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="C202" s="8" t="s">
-        <v>548</v>
       </c>
       <c r="D202" s="8" t="s">
         <v>31</v>
@@ -48354,13 +48357,13 @@
     </row>
     <row r="203" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="C203" s="8" t="s">
         <v>549</v>
-      </c>
-      <c r="B203" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="C203" s="8" t="s">
-        <v>551</v>
       </c>
       <c r="D203" s="8" t="s">
         <v>31</v>
@@ -48371,13 +48374,13 @@
     </row>
     <row r="204" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="C204" s="8" t="s">
         <v>552</v>
-      </c>
-      <c r="B204" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="C204" s="8" t="s">
-        <v>554</v>
       </c>
       <c r="D204" s="8" t="s">
         <v>31</v>
@@ -48386,15 +48389,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="C205" s="8" t="s">
         <v>555</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="C205" s="8" t="s">
-        <v>557</v>
       </c>
       <c r="D205" s="8" t="s">
         <v>31</v>
@@ -48405,13 +48408,13 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C206" s="8" t="s">
         <v>558</v>
-      </c>
-      <c r="B206" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="C206" s="8" t="s">
-        <v>560</v>
       </c>
       <c r="D206" s="8" t="s">
         <v>31</v>
@@ -48422,13 +48425,13 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="C207" s="8" t="s">
         <v>561</v>
-      </c>
-      <c r="B207" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="C207" s="8" t="s">
-        <v>563</v>
       </c>
       <c r="D207" s="8" t="s">
         <v>31</v>
@@ -48437,15 +48440,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="C208" s="8" t="s">
         <v>564</v>
-      </c>
-      <c r="B208" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="C208" s="8" t="s">
-        <v>566</v>
       </c>
       <c r="D208" s="8" t="s">
         <v>31</v>
@@ -48454,15 +48457,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="C209" s="8" t="s">
         <v>567</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="C209" s="8" t="s">
-        <v>569</v>
       </c>
       <c r="D209" s="8" t="s">
         <v>31</v>
@@ -48471,15 +48474,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="C210" s="8" t="s">
         <v>570</v>
-      </c>
-      <c r="B210" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="C210" s="8" t="s">
-        <v>572</v>
       </c>
       <c r="D210" s="8" t="s">
         <v>31</v>
@@ -48488,15 +48491,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C211" s="8" t="s">
         <v>573</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>574</v>
-      </c>
-      <c r="C211" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="D211" s="8" t="s">
         <v>31</v>
@@ -48507,13 +48510,13 @@
     </row>
     <row r="212" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="C212" s="8" t="s">
         <v>576</v>
-      </c>
-      <c r="B212" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="C212" s="8" t="s">
-        <v>578</v>
       </c>
       <c r="D212" s="8" t="s">
         <v>31</v>
@@ -48522,15 +48525,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C213" s="8" t="s">
         <v>579</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>580</v>
-      </c>
-      <c r="C213" s="8" t="s">
-        <v>581</v>
       </c>
       <c r="D213" s="8" t="s">
         <v>31</v>
@@ -48539,15 +48542,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="C214" s="8" t="s">
         <v>582</v>
-      </c>
-      <c r="B214" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="C214" s="8" t="s">
-        <v>584</v>
       </c>
       <c r="D214" s="8" t="s">
         <v>31</v>
@@ -48558,13 +48561,13 @@
     </row>
     <row r="215" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C215" s="8" t="s">
         <v>585</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="C215" s="8" t="s">
-        <v>587</v>
       </c>
       <c r="D215" s="8" t="s">
         <v>31</v>
@@ -48575,13 +48578,13 @@
     </row>
     <row r="216" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="C216" s="8" t="s">
         <v>588</v>
-      </c>
-      <c r="B216" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="C216" s="8" t="s">
-        <v>590</v>
       </c>
       <c r="D216" s="8" t="s">
         <v>31</v>
@@ -48590,49 +48593,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="C217" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="B217" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="C217" s="8" t="s">
+      <c r="D217" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="B218" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="D217" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="E217" s="8" t="s">
+      <c r="C218" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="D218" s="8" t="s">
         <v>593</v>
       </c>
+      <c r="E218" s="8" t="s">
+        <v>594</v>
+      </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="B218" s="9" t="s">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="8" t="s">
         <v>595</v>
       </c>
-      <c r="C218" s="8" t="s">
+      <c r="B219" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="D218" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E218" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="8" t="s">
+      <c r="C219" s="8" t="s">
         <v>597</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="C219" s="8" t="s">
-        <v>599</v>
       </c>
       <c r="D219" s="8" t="s">
         <v>31</v>
@@ -48643,13 +48646,13 @@
     </row>
     <row r="220" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="B220" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="C220" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="B220" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="C220" s="8" t="s">
-        <v>602</v>
       </c>
       <c r="D220" s="8" t="s">
         <v>31</v>
@@ -48660,13 +48663,13 @@
     </row>
     <row r="221" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="C221" s="8" t="s">
         <v>603</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="C221" s="8" t="s">
-        <v>605</v>
       </c>
       <c r="D221" s="8" t="s">
         <v>31</v>
@@ -48677,13 +48680,13 @@
     </row>
     <row r="222" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="C222" s="8" t="s">
         <v>606</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="C222" s="8" t="s">
-        <v>608</v>
       </c>
       <c r="D222" s="8" t="s">
         <v>31</v>
@@ -48694,13 +48697,13 @@
     </row>
     <row r="223" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="C223" s="8" t="s">
         <v>609</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="C223" s="8" t="s">
-        <v>611</v>
       </c>
       <c r="D223" s="8" t="s">
         <v>31</v>
@@ -48711,13 +48714,13 @@
     </row>
     <row r="224" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="C224" s="8" t="s">
         <v>612</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="C224" s="8" t="s">
-        <v>614</v>
       </c>
       <c r="D224" s="8" t="s">
         <v>31</v>
@@ -48728,13 +48731,13 @@
     </row>
     <row r="225" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="C225" s="8" t="s">
         <v>615</v>
-      </c>
-      <c r="B225" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="C225" s="8" t="s">
-        <v>617</v>
       </c>
       <c r="D225" s="8" t="s">
         <v>31</v>
@@ -48743,15 +48746,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B226" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="C226" s="8" t="s">
         <v>618</v>
-      </c>
-      <c r="B226" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="C226" s="8" t="s">
-        <v>620</v>
       </c>
       <c r="D226" s="8" t="s">
         <v>31</v>
@@ -48760,15 +48763,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="C227" s="8" t="s">
         <v>621</v>
-      </c>
-      <c r="B227" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="C227" s="8" t="s">
-        <v>623</v>
       </c>
       <c r="D227" s="8" t="s">
         <v>31</v>
@@ -48779,13 +48782,13 @@
     </row>
     <row r="228" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="C228" s="8" t="s">
         <v>624</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="C228" s="8" t="s">
-        <v>626</v>
       </c>
       <c r="D228" s="8" t="s">
         <v>31</v>
@@ -48796,13 +48799,13 @@
     </row>
     <row r="229" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C229" s="8" t="s">
         <v>627</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="C229" s="8" t="s">
-        <v>629</v>
       </c>
       <c r="D229" s="8" t="s">
         <v>31</v>
@@ -48813,13 +48816,13 @@
     </row>
     <row r="230" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="C230" s="8" t="s">
         <v>630</v>
-      </c>
-      <c r="B230" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="C230" s="8" t="s">
-        <v>632</v>
       </c>
       <c r="D230" s="8" t="s">
         <v>31</v>
@@ -48830,13 +48833,13 @@
     </row>
     <row r="231" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="C231" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="B231" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="C231" s="8" t="s">
-        <v>635</v>
       </c>
       <c r="D231" s="8" t="s">
         <v>31</v>
@@ -48847,13 +48850,13 @@
     </row>
     <row r="232" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="C232" s="8" t="s">
         <v>636</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="C232" s="8" t="s">
-        <v>638</v>
       </c>
       <c r="D232" s="8" t="s">
         <v>31</v>
@@ -48864,13 +48867,13 @@
     </row>
     <row r="233" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C233" s="8" t="s">
         <v>639</v>
-      </c>
-      <c r="B233" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="C233" s="8" t="s">
-        <v>641</v>
       </c>
       <c r="D233" s="8" t="s">
         <v>31</v>
@@ -48881,13 +48884,13 @@
     </row>
     <row r="234" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="C234" s="8" t="s">
         <v>642</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="C234" s="8" t="s">
-        <v>644</v>
       </c>
       <c r="D234" s="8" t="s">
         <v>31</v>
@@ -48898,13 +48901,13 @@
     </row>
     <row r="235" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C235" s="8" t="s">
         <v>645</v>
-      </c>
-      <c r="B235" s="9" t="s">
-        <v>646</v>
-      </c>
-      <c r="C235" s="8" t="s">
-        <v>647</v>
       </c>
       <c r="D235" s="8" t="s">
         <v>31</v>
@@ -48913,15 +48916,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="B236" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="C236" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="B236" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="C236" s="8" t="s">
-        <v>650</v>
       </c>
       <c r="D236" s="8" t="s">
         <v>31</v>
@@ -48932,13 +48935,13 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="C237" s="8" t="s">
         <v>651</v>
-      </c>
-      <c r="B237" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="C237" s="8" t="s">
-        <v>653</v>
       </c>
       <c r="D237" s="8" t="s">
         <v>31</v>
@@ -48949,13 +48952,13 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="C238" s="8" t="s">
         <v>654</v>
-      </c>
-      <c r="B238" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="C238" s="8" t="s">
-        <v>655</v>
       </c>
       <c r="D238" s="8" t="s">
         <v>31</v>
@@ -48966,13 +48969,13 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="C239" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="B239" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="C239" s="8" t="s">
-        <v>657</v>
       </c>
       <c r="D239" s="8" t="s">
         <v>31</v>
@@ -48981,15 +48984,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="C240" s="8" t="s">
         <v>658</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>659</v>
-      </c>
-      <c r="C240" s="8" t="s">
-        <v>660</v>
       </c>
       <c r="D240" s="8" t="s">
         <v>31</v>
@@ -48998,15 +49001,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="C241" s="8" t="s">
         <v>661</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>662</v>
-      </c>
-      <c r="C241" s="8" t="s">
-        <v>663</v>
       </c>
       <c r="D241" s="8" t="s">
         <v>31</v>
@@ -49015,15 +49018,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="C242" s="8" t="s">
         <v>664</v>
-      </c>
-      <c r="B242" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="C242" s="8" t="s">
-        <v>666</v>
       </c>
       <c r="D242" s="8" t="s">
         <v>31</v>
@@ -49032,15 +49035,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="C243" s="8" t="s">
         <v>667</v>
-      </c>
-      <c r="B243" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="C243" s="8" t="s">
-        <v>669</v>
       </c>
       <c r="D243" s="8" t="s">
         <v>31</v>
@@ -49051,13 +49054,13 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="B244" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="C244" s="8" t="s">
         <v>670</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="C244" s="8" t="s">
-        <v>672</v>
       </c>
       <c r="D244" s="8" t="s">
         <v>31</v>
@@ -49068,13 +49071,13 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="C245" s="8" t="s">
         <v>673</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="C245" s="8" t="s">
-        <v>675</v>
       </c>
       <c r="D245" s="8" t="s">
         <v>31</v>
@@ -49083,15 +49086,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="C246" s="8" t="s">
         <v>676</v>
-      </c>
-      <c r="B246" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="C246" s="8" t="s">
-        <v>678</v>
       </c>
       <c r="D246" s="8" t="s">
         <v>31</v>
@@ -49102,13 +49105,13 @@
     </row>
     <row r="247" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="C247" s="8" t="s">
         <v>679</v>
-      </c>
-      <c r="B247" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="C247" s="8" t="s">
-        <v>681</v>
       </c>
       <c r="D247" s="8" t="s">
         <v>31</v>
@@ -49117,15 +49120,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B248" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="C248" s="8" t="s">
         <v>682</v>
-      </c>
-      <c r="B248" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="C248" s="8" t="s">
-        <v>684</v>
       </c>
       <c r="D248" s="8" t="s">
         <v>31</v>
@@ -49134,15 +49137,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="C249" s="8" t="s">
         <v>685</v>
-      </c>
-      <c r="B249" s="9" t="s">
-        <v>686</v>
-      </c>
-      <c r="C249" s="8" t="s">
-        <v>687</v>
       </c>
       <c r="D249" s="8" t="s">
         <v>31</v>
@@ -49151,15 +49154,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="C250" s="8" t="s">
         <v>688</v>
-      </c>
-      <c r="B250" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="C250" s="8" t="s">
-        <v>690</v>
       </c>
       <c r="D250" s="8" t="s">
         <v>31</v>
@@ -49170,13 +49173,13 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="C251" s="8" t="s">
         <v>691</v>
-      </c>
-      <c r="B251" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="C251" s="8" t="s">
-        <v>693</v>
       </c>
       <c r="D251" s="8" t="s">
         <v>31</v>
@@ -49185,15 +49188,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="B252" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="C252" s="8" t="s">
         <v>694</v>
-      </c>
-      <c r="B252" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="C252" s="8" t="s">
-        <v>696</v>
       </c>
       <c r="D252" s="8" t="s">
         <v>31</v>
@@ -49202,15 +49205,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="C253" s="8" t="s">
         <v>697</v>
-      </c>
-      <c r="B253" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="C253" s="8" t="s">
-        <v>699</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>31</v>
@@ -49219,15 +49222,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="C254" s="8" t="s">
         <v>700</v>
-      </c>
-      <c r="B254" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="C254" s="8" t="s">
-        <v>702</v>
       </c>
       <c r="D254" s="8" t="s">
         <v>31</v>
@@ -49238,13 +49241,13 @@
     </row>
     <row r="255" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="C255" s="8" t="s">
         <v>703</v>
-      </c>
-      <c r="B255" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="C255" s="8" t="s">
-        <v>705</v>
       </c>
       <c r="D255" s="8" t="s">
         <v>31</v>
@@ -49255,13 +49258,13 @@
     </row>
     <row r="256" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="B256" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="C256" s="8" t="s">
         <v>706</v>
-      </c>
-      <c r="B256" s="9" t="s">
-        <v>707</v>
-      </c>
-      <c r="C256" s="8" t="s">
-        <v>708</v>
       </c>
       <c r="D256" s="8" t="s">
         <v>31</v>
@@ -49270,15 +49273,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="C257" s="8" t="s">
         <v>709</v>
-      </c>
-      <c r="B257" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="C257" s="8" t="s">
-        <v>711</v>
       </c>
       <c r="D257" s="8" t="s">
         <v>31</v>
@@ -49287,15 +49290,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="C258" s="8" t="s">
         <v>712</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="C258" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="D258" s="8" t="s">
         <v>31</v>
@@ -49306,13 +49309,13 @@
     </row>
     <row r="259" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="C259" s="8" t="s">
         <v>715</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="C259" s="8" t="s">
-        <v>714</v>
       </c>
       <c r="D259" s="8" t="s">
         <v>31</v>
@@ -49326,10 +49329,10 @@
         <v>716</v>
       </c>
       <c r="B260" s="9" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>31</v>
@@ -49340,13 +49343,13 @@
     </row>
     <row r="261" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>718</v>
+      </c>
+      <c r="C261" s="8" t="s">
         <v>719</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>720</v>
-      </c>
-      <c r="C261" s="8" t="s">
-        <v>721</v>
       </c>
       <c r="D261" s="8" t="s">
         <v>31</v>
@@ -49357,13 +49360,13 @@
     </row>
     <row r="262" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="C262" s="8" t="s">
         <v>722</v>
-      </c>
-      <c r="B262" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="C262" s="8" t="s">
-        <v>724</v>
       </c>
       <c r="D262" s="8" t="s">
         <v>31</v>
@@ -49374,13 +49377,13 @@
     </row>
     <row r="263" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="C263" s="8" t="s">
         <v>725</v>
-      </c>
-      <c r="B263" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>727</v>
       </c>
       <c r="D263" s="8" t="s">
         <v>31</v>
@@ -49391,13 +49394,13 @@
     </row>
     <row r="264" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="B264" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="C264" s="8" t="s">
         <v>728</v>
-      </c>
-      <c r="B264" s="9" t="s">
-        <v>729</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>730</v>
       </c>
       <c r="D264" s="8" t="s">
         <v>31</v>
@@ -49406,15 +49409,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>730</v>
+      </c>
+      <c r="C265" s="8" t="s">
         <v>731</v>
-      </c>
-      <c r="B265" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="C265" s="8" t="s">
-        <v>733</v>
       </c>
       <c r="D265" s="8" t="s">
         <v>31</v>
@@ -49423,15 +49426,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="C266" s="8" t="s">
         <v>734</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="C266" s="8" t="s">
-        <v>736</v>
       </c>
       <c r="D266" s="8" t="s">
         <v>31</v>
@@ -49440,15 +49443,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="C267" s="8" t="s">
         <v>737</v>
-      </c>
-      <c r="B267" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="C267" s="8" t="s">
-        <v>739</v>
       </c>
       <c r="D267" s="8" t="s">
         <v>31</v>
@@ -49457,15 +49460,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B268" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="C268" s="8" t="s">
         <v>740</v>
-      </c>
-      <c r="B268" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="C268" s="8" t="s">
-        <v>742</v>
       </c>
       <c r="D268" s="8" t="s">
         <v>31</v>
@@ -49474,15 +49477,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="C269" s="8" t="s">
         <v>743</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="C269" s="8" t="s">
-        <v>745</v>
       </c>
       <c r="D269" s="8" t="s">
         <v>31</v>
@@ -49493,13 +49496,13 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="B270" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="C270" s="8" t="s">
         <v>746</v>
-      </c>
-      <c r="B270" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="C270" s="8" t="s">
-        <v>748</v>
       </c>
       <c r="D270" s="8" t="s">
         <v>31</v>
@@ -49508,15 +49511,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="C271" s="8" t="s">
         <v>749</v>
-      </c>
-      <c r="B271" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="C271" s="8" t="s">
-        <v>751</v>
       </c>
       <c r="D271" s="8" t="s">
         <v>31</v>
@@ -49525,15 +49528,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="C272" s="8" t="s">
         <v>752</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>753</v>
-      </c>
-      <c r="C272" s="8" t="s">
-        <v>754</v>
       </c>
       <c r="D272" s="8" t="s">
         <v>31</v>
@@ -49544,13 +49547,13 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="B273" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="C273" s="8" t="s">
         <v>755</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="C273" s="8" t="s">
-        <v>757</v>
       </c>
       <c r="D273" s="8" t="s">
         <v>31</v>
@@ -49561,13 +49564,13 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="B274" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="C274" s="8" t="s">
         <v>758</v>
-      </c>
-      <c r="B274" s="9" t="s">
-        <v>759</v>
-      </c>
-      <c r="C274" s="8" t="s">
-        <v>760</v>
       </c>
       <c r="D274" s="8" t="s">
         <v>31</v>
@@ -49578,13 +49581,13 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="C275" s="8" t="s">
         <v>761</v>
-      </c>
-      <c r="B275" s="9" t="s">
-        <v>762</v>
-      </c>
-      <c r="C275" s="8" t="s">
-        <v>763</v>
       </c>
       <c r="D275" s="8" t="s">
         <v>31</v>
@@ -49595,13 +49598,13 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B276" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="C276" s="8" t="s">
         <v>764</v>
-      </c>
-      <c r="B276" s="9" t="s">
-        <v>765</v>
-      </c>
-      <c r="C276" s="8" t="s">
-        <v>766</v>
       </c>
       <c r="D276" s="8" t="s">
         <v>31</v>
@@ -49612,13 +49615,13 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="B277" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="C277" s="8" t="s">
         <v>767</v>
-      </c>
-      <c r="B277" s="9" t="s">
-        <v>768</v>
-      </c>
-      <c r="C277" s="8" t="s">
-        <v>769</v>
       </c>
       <c r="D277" s="8" t="s">
         <v>31</v>
@@ -49629,13 +49632,13 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="B278" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="C278" s="8" t="s">
         <v>770</v>
-      </c>
-      <c r="B278" s="9" t="s">
-        <v>771</v>
-      </c>
-      <c r="C278" s="8" t="s">
-        <v>772</v>
       </c>
       <c r="D278" s="8" t="s">
         <v>31</v>
@@ -49644,15 +49647,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="B279" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="C279" s="8" t="s">
         <v>773</v>
-      </c>
-      <c r="B279" s="9" t="s">
-        <v>774</v>
-      </c>
-      <c r="C279" s="8" t="s">
-        <v>775</v>
       </c>
       <c r="D279" s="8" t="s">
         <v>31</v>
@@ -49663,13 +49666,13 @@
     </row>
     <row r="280" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="B280" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="C280" s="8" t="s">
         <v>776</v>
-      </c>
-      <c r="B280" s="9" t="s">
-        <v>777</v>
-      </c>
-      <c r="C280" s="8" t="s">
-        <v>778</v>
       </c>
       <c r="D280" s="8" t="s">
         <v>31</v>
@@ -49680,13 +49683,13 @@
     </row>
     <row r="281" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="B281" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="C281" s="8" t="s">
         <v>779</v>
-      </c>
-      <c r="B281" s="9" t="s">
-        <v>780</v>
-      </c>
-      <c r="C281" s="8" t="s">
-        <v>781</v>
       </c>
       <c r="D281" s="8" t="s">
         <v>31</v>
@@ -49697,13 +49700,13 @@
     </row>
     <row r="282" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="B282" s="9" t="s">
+        <v>781</v>
+      </c>
+      <c r="C282" s="8" t="s">
         <v>782</v>
-      </c>
-      <c r="B282" s="9" t="s">
-        <v>783</v>
-      </c>
-      <c r="C282" s="8" t="s">
-        <v>784</v>
       </c>
       <c r="D282" s="8" t="s">
         <v>31</v>
@@ -49714,13 +49717,13 @@
     </row>
     <row r="283" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="C283" s="8" t="s">
         <v>785</v>
-      </c>
-      <c r="B283" s="9" t="s">
-        <v>786</v>
-      </c>
-      <c r="C283" s="8" t="s">
-        <v>787</v>
       </c>
       <c r="D283" s="8" t="s">
         <v>31</v>
@@ -49731,13 +49734,13 @@
     </row>
     <row r="284" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="B284" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="C284" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="B284" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="C284" s="8" t="s">
-        <v>790</v>
       </c>
       <c r="D284" s="8" t="s">
         <v>31</v>
@@ -49748,13 +49751,13 @@
     </row>
     <row r="285" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="C285" s="8" t="s">
         <v>791</v>
-      </c>
-      <c r="B285" s="9" t="s">
-        <v>792</v>
-      </c>
-      <c r="C285" s="8" t="s">
-        <v>793</v>
       </c>
       <c r="D285" s="8" t="s">
         <v>31</v>
@@ -49765,13 +49768,13 @@
     </row>
     <row r="286" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B286" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="C286" s="8" t="s">
         <v>794</v>
-      </c>
-      <c r="B286" s="9" t="s">
-        <v>795</v>
-      </c>
-      <c r="C286" s="8" t="s">
-        <v>796</v>
       </c>
       <c r="D286" s="8" t="s">
         <v>31</v>
@@ -49782,13 +49785,13 @@
     </row>
     <row r="287" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="B287" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="C287" s="8" t="s">
         <v>797</v>
-      </c>
-      <c r="B287" s="9" t="s">
-        <v>798</v>
-      </c>
-      <c r="C287" s="8" t="s">
-        <v>799</v>
       </c>
       <c r="D287" s="8" t="s">
         <v>31</v>
@@ -49797,15 +49800,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="8" t="s">
+        <v>798</v>
+      </c>
+      <c r="B288" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="C288" s="8" t="s">
         <v>800</v>
-      </c>
-      <c r="B288" s="9" t="s">
-        <v>801</v>
-      </c>
-      <c r="C288" s="8" t="s">
-        <v>799</v>
       </c>
       <c r="D288" s="8" t="s">
         <v>31</v>
@@ -49814,15 +49817,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B289" s="9" t="s">
         <v>802</v>
       </c>
-      <c r="B289" s="9" t="s">
-        <v>803</v>
-      </c>
       <c r="C289" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D289" s="8" t="s">
         <v>31</v>
@@ -49833,13 +49836,13 @@
     </row>
     <row r="290" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="B290" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="B290" s="9" t="s">
-        <v>805</v>
-      </c>
       <c r="C290" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D290" s="8" t="s">
         <v>31</v>
@@ -49850,13 +49853,13 @@
     </row>
     <row r="291" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="B291" s="9" t="s">
         <v>806</v>
       </c>
-      <c r="B291" s="9" t="s">
-        <v>807</v>
-      </c>
       <c r="C291" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D291" s="8" t="s">
         <v>31</v>
@@ -49867,13 +49870,13 @@
     </row>
     <row r="292" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="B292" s="9" t="s">
         <v>808</v>
       </c>
-      <c r="B292" s="9" t="s">
-        <v>809</v>
-      </c>
       <c r="C292" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D292" s="8" t="s">
         <v>31</v>
@@ -49884,13 +49887,13 @@
     </row>
     <row r="293" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B293" s="9" t="s">
         <v>810</v>
       </c>
-      <c r="B293" s="9" t="s">
-        <v>811</v>
-      </c>
       <c r="C293" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D293" s="8" t="s">
         <v>31</v>
@@ -49901,13 +49904,13 @@
     </row>
     <row r="294" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="B294" s="9" t="s">
         <v>812</v>
       </c>
-      <c r="B294" s="9" t="s">
-        <v>813</v>
-      </c>
       <c r="C294" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D294" s="8" t="s">
         <v>31</v>
@@ -49918,13 +49921,13 @@
     </row>
     <row r="295" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="B295" s="9" t="s">
         <v>814</v>
       </c>
-      <c r="B295" s="9" t="s">
-        <v>815</v>
-      </c>
       <c r="C295" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D295" s="8" t="s">
         <v>31</v>
@@ -49933,15 +49936,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B296" s="9" t="s">
         <v>816</v>
       </c>
-      <c r="B296" s="9" t="s">
-        <v>817</v>
-      </c>
       <c r="C296" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D296" s="8" t="s">
         <v>31</v>
@@ -49950,15 +49953,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B297" s="9" t="s">
         <v>818</v>
       </c>
-      <c r="B297" s="9" t="s">
-        <v>819</v>
-      </c>
       <c r="C297" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D297" s="8" t="s">
         <v>31</v>
@@ -49967,15 +49970,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="B298" s="9" t="s">
         <v>820</v>
       </c>
-      <c r="B298" s="9" t="s">
-        <v>821</v>
-      </c>
       <c r="C298" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D298" s="8" t="s">
         <v>31</v>
@@ -49986,13 +49989,13 @@
     </row>
     <row r="299" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="B299" s="9" t="s">
         <v>822</v>
       </c>
-      <c r="B299" s="9" t="s">
-        <v>823</v>
-      </c>
       <c r="C299" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D299" s="8" t="s">
         <v>31</v>
@@ -50001,15 +50004,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="38.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B300" s="9" t="s">
         <v>824</v>
       </c>
-      <c r="B300" s="9" t="s">
-        <v>825</v>
-      </c>
       <c r="C300" s="8" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D300" s="8" t="s">
         <v>31</v>
@@ -50018,15 +50021,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="B301" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="B301" s="9" t="s">
-        <v>827</v>
-      </c>
       <c r="C301" s="8" t="s">
-        <v>828</v>
+        <v>800</v>
       </c>
       <c r="D301" s="8" t="s">
         <v>31</v>
@@ -50037,13 +50040,13 @@
     </row>
     <row r="302" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B302" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="C302" s="8" t="s">
         <v>829</v>
-      </c>
-      <c r="B302" s="9" t="s">
-        <v>830</v>
-      </c>
-      <c r="C302" s="8" t="s">
-        <v>831</v>
       </c>
       <c r="D302" s="8" t="s">
         <v>31</v>
@@ -50054,13 +50057,13 @@
     </row>
     <row r="303" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="8" t="s">
+        <v>830</v>
+      </c>
+      <c r="B303" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="C303" s="8" t="s">
         <v>832</v>
-      </c>
-      <c r="B303" s="9" t="s">
-        <v>833</v>
-      </c>
-      <c r="C303" s="8" t="s">
-        <v>834</v>
       </c>
       <c r="D303" s="8" t="s">
         <v>31</v>
@@ -50071,13 +50074,13 @@
     </row>
     <row r="304" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="B304" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="C304" s="8" t="s">
         <v>835</v>
-      </c>
-      <c r="B304" s="9" t="s">
-        <v>836</v>
-      </c>
-      <c r="C304" s="8" t="s">
-        <v>837</v>
       </c>
       <c r="D304" s="8" t="s">
         <v>31</v>
@@ -50086,15 +50089,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="8" t="s">
+        <v>836</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="C305" s="8" t="s">
         <v>838</v>
-      </c>
-      <c r="B305" s="9" t="s">
-        <v>839</v>
-      </c>
-      <c r="C305" s="8" t="s">
-        <v>840</v>
       </c>
       <c r="D305" s="8" t="s">
         <v>31</v>
@@ -50103,15 +50106,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B306" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="C306" s="8" t="s">
         <v>841</v>
-      </c>
-      <c r="B306" s="9" t="s">
-        <v>842</v>
-      </c>
-      <c r="C306" s="8" t="s">
-        <v>843</v>
       </c>
       <c r="D306" s="8" t="s">
         <v>31</v>
@@ -50122,13 +50125,13 @@
     </row>
     <row r="307" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="B307" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="C307" s="8" t="s">
         <v>844</v>
-      </c>
-      <c r="B307" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="C307" s="8" t="s">
-        <v>846</v>
       </c>
       <c r="D307" s="8" t="s">
         <v>31</v>
@@ -50137,32 +50140,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="11" t="s">
+    <row r="308" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A308" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B308" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="C308" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="B308" s="10" t="s">
-        <v>848</v>
-      </c>
-      <c r="C308" s="10" t="s">
-        <v>849</v>
-      </c>
-      <c r="D308" s="10" t="s">
+      <c r="D308" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E308" s="10" t="s">
+      <c r="E308" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="11" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B309" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="C309" s="10" t="s">
         <v>850</v>
-      </c>
-      <c r="C309" s="10" t="s">
-        <v>849</v>
       </c>
       <c r="D309" s="10" t="s">
         <v>31</v>
@@ -50173,13 +50176,13 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="11" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B310" s="10" t="s">
         <v>851</v>
       </c>
       <c r="C310" s="10" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D310" s="10" t="s">
         <v>31</v>
@@ -50188,32 +50191,32 @@
         <v>32</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="9" t="s">
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="B311" s="10" t="s">
         <v>852</v>
       </c>
-      <c r="B311" s="9" t="s">
+      <c r="C311" s="10" t="s">
+        <v>850</v>
+      </c>
+      <c r="D311" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E311" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="B312" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C311" s="8" t="s">
+      <c r="C312" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="D311" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E311" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="312" customFormat="false" ht="114.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="9" t="s">
-        <v>852</v>
-      </c>
-      <c r="B312" s="9" t="s">
-        <v>853</v>
-      </c>
-      <c r="C312" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="D312" s="8" t="s">
         <v>31</v>
@@ -50222,15 +50225,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="114.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="B313" s="9" t="s">
         <v>854</v>
       </c>
-      <c r="B313" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="C313" s="8" t="s">
-        <v>189</v>
+        <v>67</v>
       </c>
       <c r="D313" s="8" t="s">
         <v>31</v>
@@ -50239,15 +50242,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="9" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>855</v>
+        <v>69</v>
       </c>
       <c r="C314" s="8" t="s">
-        <v>856</v>
+        <v>189</v>
       </c>
       <c r="D314" s="8" t="s">
         <v>31</v>
@@ -50256,15 +50259,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B315" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="C315" s="8" t="s">
         <v>857</v>
-      </c>
-      <c r="B315" s="9" t="s">
-        <v>858</v>
-      </c>
-      <c r="C315" s="8" t="s">
-        <v>859</v>
       </c>
       <c r="D315" s="8" t="s">
         <v>31</v>
@@ -50275,13 +50278,13 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="B316" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="C316" s="8" t="s">
         <v>860</v>
-      </c>
-      <c r="B316" s="9" t="s">
-        <v>861</v>
-      </c>
-      <c r="C316" s="8" t="s">
-        <v>862</v>
       </c>
       <c r="D316" s="8" t="s">
         <v>31</v>
@@ -50292,13 +50295,13 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="B317" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="C317" s="8" t="s">
         <v>863</v>
-      </c>
-      <c r="B317" s="9" t="s">
-        <v>864</v>
-      </c>
-      <c r="C317" s="8" t="s">
-        <v>865</v>
       </c>
       <c r="D317" s="8" t="s">
         <v>31</v>
@@ -50308,14 +50311,14 @@
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="8" t="s">
+      <c r="A318" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="B318" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="C318" s="8" t="s">
         <v>866</v>
-      </c>
-      <c r="B318" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="C318" s="8" t="s">
-        <v>868</v>
       </c>
       <c r="D318" s="8" t="s">
         <v>31</v>
@@ -50326,13 +50329,13 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="8" t="s">
-        <v>111</v>
+        <v>867</v>
       </c>
       <c r="B319" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="C319" s="8" t="s">
         <v>869</v>
-      </c>
-      <c r="C319" s="8" t="s">
-        <v>870</v>
       </c>
       <c r="D319" s="8" t="s">
         <v>31</v>
@@ -50341,15 +50344,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="66.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="8" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="B320" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="C320" s="8" t="s">
         <v>871</v>
-      </c>
-      <c r="C320" s="8" t="s">
-        <v>872</v>
       </c>
       <c r="D320" s="8" t="s">
         <v>31</v>
@@ -50358,15 +50361,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="66.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="8" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B321" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="C321" s="8" t="s">
         <v>873</v>
-      </c>
-      <c r="C321" s="8" t="s">
-        <v>874</v>
       </c>
       <c r="D321" s="8" t="s">
         <v>31</v>
@@ -50375,15 +50378,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B322" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="C322" s="8" t="s">
         <v>875</v>
-      </c>
-      <c r="B322" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="C322" s="8" t="s">
-        <v>877</v>
       </c>
       <c r="D322" s="8" t="s">
         <v>31</v>
@@ -50392,15 +50395,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="B323" s="9" t="s">
+        <v>877</v>
+      </c>
+      <c r="C323" s="8" t="s">
         <v>878</v>
-      </c>
-      <c r="B323" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="C323" s="8" t="s">
-        <v>880</v>
       </c>
       <c r="D323" s="8" t="s">
         <v>31</v>
@@ -50409,15 +50412,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="91.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="B324" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="C324" s="8" t="s">
         <v>881</v>
-      </c>
-      <c r="B324" s="9" t="s">
-        <v>882</v>
-      </c>
-      <c r="C324" s="8" t="s">
-        <v>883</v>
       </c>
       <c r="D324" s="8" t="s">
         <v>31</v>
@@ -50426,15 +50429,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="91.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="C325" s="8" t="s">
         <v>884</v>
-      </c>
-      <c r="B325" s="9" t="s">
-        <v>885</v>
-      </c>
-      <c r="C325" s="8" t="s">
-        <v>886</v>
       </c>
       <c r="D325" s="8" t="s">
         <v>31</v>
@@ -50443,15 +50446,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="B326" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="C326" s="8" t="s">
         <v>887</v>
-      </c>
-      <c r="B326" s="9" t="s">
-        <v>888</v>
-      </c>
-      <c r="C326" s="8" t="s">
-        <v>889</v>
       </c>
       <c r="D326" s="8" t="s">
         <v>31</v>
@@ -50461,31 +50464,31 @@
       </c>
     </row>
     <row r="327" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="10" t="s">
+      <c r="A327" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="B327" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="C327" s="8" t="s">
         <v>890</v>
       </c>
-      <c r="B327" s="11" t="s">
-        <v>891</v>
-      </c>
-      <c r="C327" s="10" t="s">
-        <v>892</v>
-      </c>
-      <c r="D327" s="10" t="s">
+      <c r="D327" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E327" s="10" t="s">
+      <c r="E327" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="10" t="s">
+        <v>891</v>
+      </c>
+      <c r="B328" s="11" t="s">
+        <v>892</v>
+      </c>
+      <c r="C328" s="10" t="s">
         <v>893</v>
-      </c>
-      <c r="B328" s="11" t="s">
-        <v>894</v>
-      </c>
-      <c r="C328" s="10" t="s">
-        <v>892</v>
       </c>
       <c r="D328" s="10" t="s">
         <v>31</v>
@@ -50496,13 +50499,13 @@
     </row>
     <row r="329" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="10" t="s">
+        <v>894</v>
+      </c>
+      <c r="B329" s="11" t="s">
         <v>895</v>
       </c>
-      <c r="B329" s="11" t="s">
-        <v>896</v>
-      </c>
       <c r="C329" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D329" s="10" t="s">
         <v>31</v>
@@ -50513,13 +50516,13 @@
     </row>
     <row r="330" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="B330" s="11" t="s">
         <v>897</v>
       </c>
-      <c r="B330" s="11" t="s">
-        <v>898</v>
-      </c>
       <c r="C330" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D330" s="10" t="s">
         <v>31</v>
@@ -50530,13 +50533,13 @@
     </row>
     <row r="331" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="10" t="s">
+        <v>898</v>
+      </c>
+      <c r="B331" s="11" t="s">
         <v>899</v>
       </c>
-      <c r="B331" s="11" t="s">
-        <v>900</v>
-      </c>
       <c r="C331" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D331" s="10" t="s">
         <v>31</v>
@@ -50547,13 +50550,13 @@
     </row>
     <row r="332" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="B332" s="11" t="s">
         <v>901</v>
       </c>
-      <c r="B332" s="11" t="s">
-        <v>902</v>
-      </c>
       <c r="C332" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D332" s="10" t="s">
         <v>31</v>
@@ -50564,13 +50567,13 @@
     </row>
     <row r="333" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="10" t="s">
+        <v>902</v>
+      </c>
+      <c r="B333" s="11" t="s">
         <v>903</v>
       </c>
-      <c r="B333" s="11" t="s">
-        <v>904</v>
-      </c>
       <c r="C333" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D333" s="10" t="s">
         <v>31</v>
@@ -50581,13 +50584,13 @@
     </row>
     <row r="334" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="B334" s="11" t="s">
         <v>905</v>
       </c>
-      <c r="B334" s="11" t="s">
-        <v>906</v>
-      </c>
       <c r="C334" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D334" s="10" t="s">
         <v>31</v>
@@ -50598,13 +50601,13 @@
     </row>
     <row r="335" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="B335" s="11" t="s">
         <v>907</v>
       </c>
-      <c r="B335" s="11" t="s">
-        <v>908</v>
-      </c>
       <c r="C335" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D335" s="10" t="s">
         <v>31</v>
@@ -50615,13 +50618,13 @@
     </row>
     <row r="336" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="10" t="s">
+        <v>908</v>
+      </c>
+      <c r="B336" s="11" t="s">
         <v>909</v>
       </c>
-      <c r="B336" s="11" t="s">
-        <v>910</v>
-      </c>
       <c r="C336" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D336" s="10" t="s">
         <v>31</v>
@@ -50632,13 +50635,13 @@
     </row>
     <row r="337" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="B337" s="11" t="s">
         <v>911</v>
       </c>
-      <c r="B337" s="11" t="s">
-        <v>912</v>
-      </c>
       <c r="C337" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D337" s="10" t="s">
         <v>31</v>
@@ -50649,13 +50652,13 @@
     </row>
     <row r="338" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="10" t="s">
+        <v>912</v>
+      </c>
+      <c r="B338" s="11" t="s">
         <v>913</v>
       </c>
-      <c r="B338" s="11" t="s">
-        <v>914</v>
-      </c>
       <c r="C338" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D338" s="10" t="s">
         <v>31</v>
@@ -50665,14 +50668,14 @@
       </c>
     </row>
     <row r="339" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="11" t="s">
+      <c r="A339" s="10" t="s">
+        <v>914</v>
+      </c>
+      <c r="B339" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="B339" s="11" t="s">
-        <v>916</v>
-      </c>
       <c r="C339" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D339" s="10" t="s">
         <v>31</v>
@@ -50683,13 +50686,13 @@
     </row>
     <row r="340" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="11" t="s">
+        <v>916</v>
+      </c>
+      <c r="B340" s="11" t="s">
         <v>917</v>
       </c>
-      <c r="B340" s="11" t="s">
-        <v>918</v>
-      </c>
       <c r="C340" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D340" s="10" t="s">
         <v>31</v>
@@ -50699,14 +50702,14 @@
       </c>
     </row>
     <row r="341" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="10" t="s">
+      <c r="A341" s="11" t="s">
+        <v>918</v>
+      </c>
+      <c r="B341" s="11" t="s">
         <v>919</v>
       </c>
-      <c r="B341" s="11" t="s">
-        <v>920</v>
-      </c>
       <c r="C341" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D341" s="10" t="s">
         <v>31</v>
@@ -50717,13 +50720,13 @@
     </row>
     <row r="342" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="10" t="s">
+        <v>920</v>
+      </c>
+      <c r="B342" s="11" t="s">
         <v>921</v>
       </c>
-      <c r="B342" s="11" t="s">
-        <v>922</v>
-      </c>
       <c r="C342" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D342" s="10" t="s">
         <v>31</v>
@@ -50734,13 +50737,13 @@
     </row>
     <row r="343" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="B343" s="11" t="s">
         <v>923</v>
       </c>
-      <c r="B343" s="11" t="s">
-        <v>924</v>
-      </c>
       <c r="C343" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D343" s="10" t="s">
         <v>31</v>
@@ -50751,13 +50754,13 @@
     </row>
     <row r="344" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="10" t="s">
+        <v>924</v>
+      </c>
+      <c r="B344" s="11" t="s">
         <v>925</v>
       </c>
-      <c r="B344" s="11" t="s">
-        <v>926</v>
-      </c>
       <c r="C344" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D344" s="10" t="s">
         <v>31</v>
@@ -50768,13 +50771,13 @@
     </row>
     <row r="345" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="10" t="s">
+        <v>926</v>
+      </c>
+      <c r="B345" s="11" t="s">
         <v>927</v>
       </c>
-      <c r="B345" s="11" t="s">
-        <v>928</v>
-      </c>
       <c r="C345" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D345" s="10" t="s">
         <v>31</v>
@@ -50785,13 +50788,13 @@
     </row>
     <row r="346" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="10" t="s">
+        <v>928</v>
+      </c>
+      <c r="B346" s="11" t="s">
         <v>929</v>
       </c>
-      <c r="B346" s="11" t="s">
-        <v>930</v>
-      </c>
       <c r="C346" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D346" s="10" t="s">
         <v>31</v>
@@ -50802,13 +50805,13 @@
     </row>
     <row r="347" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="10" t="s">
+        <v>930</v>
+      </c>
+      <c r="B347" s="11" t="s">
         <v>931</v>
       </c>
-      <c r="B347" s="11" t="s">
-        <v>932</v>
-      </c>
       <c r="C347" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D347" s="10" t="s">
         <v>31</v>
@@ -50819,13 +50822,13 @@
     </row>
     <row r="348" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="B348" s="11" t="s">
         <v>933</v>
       </c>
-      <c r="B348" s="11" t="s">
-        <v>934</v>
-      </c>
       <c r="C348" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D348" s="10" t="s">
         <v>31</v>
@@ -50836,13 +50839,13 @@
     </row>
     <row r="349" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="10" t="s">
+        <v>934</v>
+      </c>
+      <c r="B349" s="11" t="s">
         <v>935</v>
       </c>
-      <c r="B349" s="11" t="s">
-        <v>936</v>
-      </c>
       <c r="C349" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D349" s="10" t="s">
         <v>31</v>
@@ -50853,13 +50856,13 @@
     </row>
     <row r="350" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="10" t="s">
+        <v>936</v>
+      </c>
+      <c r="B350" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="B350" s="11" t="s">
-        <v>938</v>
-      </c>
       <c r="C350" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D350" s="10" t="s">
         <v>31</v>
@@ -50870,13 +50873,13 @@
     </row>
     <row r="351" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="10" t="s">
+        <v>938</v>
+      </c>
+      <c r="B351" s="11" t="s">
         <v>939</v>
       </c>
-      <c r="B351" s="11" t="s">
-        <v>940</v>
-      </c>
       <c r="C351" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D351" s="10" t="s">
         <v>31</v>
@@ -50887,13 +50890,13 @@
     </row>
     <row r="352" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="10" t="s">
+        <v>940</v>
+      </c>
+      <c r="B352" s="11" t="s">
         <v>941</v>
       </c>
-      <c r="B352" s="11" t="s">
-        <v>942</v>
-      </c>
       <c r="C352" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D352" s="10" t="s">
         <v>31</v>
@@ -50904,13 +50907,13 @@
     </row>
     <row r="353" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="B353" s="11" t="s">
         <v>943</v>
       </c>
-      <c r="B353" s="11" t="s">
-        <v>944</v>
-      </c>
       <c r="C353" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D353" s="10" t="s">
         <v>31</v>
@@ -50920,14 +50923,14 @@
       </c>
     </row>
     <row r="354" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="11" t="s">
+      <c r="A354" s="10" t="s">
+        <v>944</v>
+      </c>
+      <c r="B354" s="11" t="s">
         <v>945</v>
       </c>
-      <c r="B354" s="11" t="s">
-        <v>946</v>
-      </c>
       <c r="C354" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D354" s="10" t="s">
         <v>31</v>
@@ -50938,13 +50941,13 @@
     </row>
     <row r="355" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="11" t="s">
+        <v>946</v>
+      </c>
+      <c r="B355" s="11" t="s">
         <v>947</v>
       </c>
-      <c r="B355" s="11" t="s">
-        <v>948</v>
-      </c>
       <c r="C355" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D355" s="10" t="s">
         <v>31</v>
@@ -50953,8 +50956,25 @@
         <v>32</v>
       </c>
     </row>
+    <row r="356" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="B356" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="C356" s="10" t="s">
+        <v>893</v>
+      </c>
+      <c r="D356" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E356" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E355"/>
+  <autoFilter ref="A1:E356"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -50983,7 +51003,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>23</v>
@@ -51028,66 +51048,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -51121,27 +51141,27 @@
         <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51149,13 +51169,13 @@
         <v>38</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51163,55 +51183,55 @@
         <v>134</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>984</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>982</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>983</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51219,27 +51239,27 @@
         <v>111</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>69</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51247,13 +51267,13 @@
         <v>127</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51261,335 +51281,335 @@
         <v>146</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
   </sheetData>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">专项检查!$A$1:$B$8</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$34</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$356</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$355</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">问题汇总!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1083">
   <si>
     <r>
       <rPr>
@@ -35340,7 +35340,7 @@
     <t xml:space="preserve">Title Page · Word count</t>
   </si>
   <si>
-    <t xml:space="preserve">2,996 … Abstract: 248 words</t>
+    <t xml:space="preserve">2,976 … Abstract: 248 words</t>
   </si>
   <si>
     <r>
@@ -35375,7 +35375,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2996</t>
+      <t xml:space="preserve">2976</t>
     </r>
     <r>
       <rPr>
@@ -35498,7 +35498,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Word count: 2,996 … Tables: 4; Figures: 3; Supplements 1–4</t>
+    <t xml:space="preserve">Word count: 2,976 … Tables: 4; Figures: 3; Supplements 1–4</t>
   </si>
   <si>
     <r>
@@ -35516,7 +35516,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2996</t>
+      <t xml:space="preserve">2976</t>
     </r>
   </si>
   <si>
@@ -37162,7 +37162,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">three of</t>
+      <t xml:space="preserve">three as</t>
     </r>
     <r>
       <rPr>
@@ -37832,61 +37832,6 @@
   </si>
   <si>
     <t xml:space="preserve">all three examinations</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">图注 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· Figure 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（计数词）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> one of</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">one of the three index</t>
-    </r>
   </si>
   <si>
     <r>
@@ -45213,7 +45158,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(核对表!B2:B2000)</f>
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45258,7 +45203,7 @@
       </c>
       <c r="B26" s="6" t="n">
         <f aca="false">COUNTIF(核对表!C2:C2000,"【定义/描述性数字】*")</f>
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45286,7 +45231,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E356"/>
+  <dimension ref="A1:E355"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -51297,7 +51242,7 @@
       </c>
     </row>
     <row r="354" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="10" t="s">
+      <c r="A354" s="11" t="s">
         <v>944</v>
       </c>
       <c r="B354" s="11" t="s">
@@ -51330,25 +51275,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="11" t="s">
-        <v>948</v>
-      </c>
-      <c r="B356" s="11" t="s">
-        <v>949</v>
-      </c>
-      <c r="C356" s="10" t="s">
-        <v>893</v>
-      </c>
-      <c r="D356" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E356" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E356"/>
+  <autoFilter ref="A1:E355"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -51377,7 +51305,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>23</v>
@@ -51422,66 +51350,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -51515,27 +51443,27 @@
         <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>966</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>967</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>968</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
+        <v>968</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>970</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>971</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>972</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51543,13 +51471,13 @@
         <v>38</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>974</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>975</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51557,13 +51485,13 @@
         <v>134</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>975</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>977</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>978</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51571,13 +51499,13 @@
         <v>277</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>980</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>981</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51585,27 +51513,27 @@
         <v>283</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>984</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>985</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>986</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>987</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51613,27 +51541,27 @@
         <v>111</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>987</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>988</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>989</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>990</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>69</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51641,13 +51569,13 @@
         <v>127</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>993</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>994</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>995</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>996</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51655,13 +51583,13 @@
         <v>146</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>996</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>997</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>998</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>999</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51669,13 +51597,13 @@
         <v>368</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>999</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>1001</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51683,13 +51611,13 @@
         <v>382</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51697,13 +51625,13 @@
         <v>385</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>1007</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51711,13 +51639,13 @@
         <v>397</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>1010</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51725,265 +51653,265 @@
         <v>406</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>1013</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>1016</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>1017</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>1020</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="D18" s="8" t="s">
         <v>1021</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>1024</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>1025</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>1028</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="D20" s="8" t="s">
         <v>1029</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>1032</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>1033</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>1036</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>1037</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>1041</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>1044</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>1045</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>1048</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>1054</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>1055</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>1061</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>1062</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>1065</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>1066</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>1069</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="D31" s="8" t="s">
         <v>1070</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>1073</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="D32" s="9" t="s">
         <v>1074</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>1077</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="D33" s="8" t="s">
         <v>1078</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>1081</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>1082</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>1084</v>
       </c>
     </row>
   </sheetData>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">专项检查!$A$1:$B$8</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$34</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$355</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$356</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">问题汇总!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="1085">
   <si>
     <r>
       <rPr>
@@ -167,7 +167,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S1–S15</t>
+      <t xml:space="preserve">S1–S19</t>
     </r>
     <r>
       <rPr>
@@ -4715,7 +4715,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S9 </t>
+      <t xml:space="preserve">S8 </t>
     </r>
     <r>
       <rPr>
@@ -19593,7 +19593,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S10</t>
+      <t xml:space="preserve">S9</t>
     </r>
     <r>
       <rPr>
@@ -20719,7 +20719,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Third portion of the duodenum (D3)</t>
+      <t xml:space="preserve">S19 · Third portion of the duodenum (D3)</t>
     </r>
   </si>
   <si>
@@ -20836,7 +20836,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Duodenojejunal junction</t>
+      <t xml:space="preserve">S19 · Duodenojejunal junction</t>
     </r>
   </si>
   <si>
@@ -20953,7 +20953,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Superior mesenteric artery–vein relationship</t>
+      <t xml:space="preserve">S19 · Superior mesenteric artery–vein relationship</t>
     </r>
   </si>
   <si>
@@ -21033,7 +21033,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Enteric fluid</t>
+      <t xml:space="preserve">S19 · Enteric fluid</t>
     </r>
   </si>
   <si>
@@ -21116,7 +21116,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Dynamic assessment</t>
+      <t xml:space="preserve">S19 · Dynamic assessment</t>
     </r>
   </si>
   <si>
@@ -21199,7 +21199,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Graded compression</t>
+      <t xml:space="preserve">S19 · Graded compression</t>
     </r>
   </si>
   <si>
@@ -21279,7 +21279,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Color Doppler of the mesenteric vessels</t>
+      <t xml:space="preserve">S19 · Color Doppler of the mesenteric vessels</t>
     </r>
   </si>
   <si>
@@ -21362,7 +21362,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Whirlpool sign</t>
+      <t xml:space="preserve">S19 · Whirlpool sign</t>
     </r>
   </si>
   <si>
@@ -21445,7 +21445,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Study adequacy</t>
+      <t xml:space="preserve">S19 · Study adequacy</t>
     </r>
   </si>
   <si>
@@ -21528,7 +21528,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Duodenum mentioned in any form</t>
+      <t xml:space="preserve">S19 · Duodenum mentioned in any form</t>
     </r>
   </si>
   <si>
@@ -21611,7 +21611,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Explicit statement of vessel inversion</t>
+      <t xml:space="preserve">S19 · Explicit statement of vessel inversion</t>
     </r>
   </si>
   <si>
@@ -21647,7 +21647,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 · Cecal position</t>
+      <t xml:space="preserve">S19 · Cecal position</t>
     </r>
   </si>
   <si>
@@ -26962,7 +26962,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Contrast enhancement</t>
+      <t xml:space="preserve">S18 · Contrast enhancement</t>
     </r>
   </si>
   <si>
@@ -27096,7 +27096,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Mesenteric whirl</t>
+      <t xml:space="preserve">S18 · Mesenteric whirl</t>
     </r>
   </si>
   <si>
@@ -27230,7 +27230,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Duodenum mentioned</t>
+      <t xml:space="preserve">S18 · Duodenum mentioned</t>
     </r>
   </si>
   <si>
@@ -27364,7 +27364,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Mesenteric-vessel relationship</t>
+      <t xml:space="preserve">S18 · Mesenteric-vessel relationship</t>
     </r>
   </si>
   <si>
@@ -27498,7 +27498,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Three-dimensional reconstruction</t>
+      <t xml:space="preserve">S18 · Three-dimensional reconstruction</t>
     </r>
   </si>
   <si>
@@ -27632,7 +27632,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Duodenojejunal junction</t>
+      <t xml:space="preserve">S18 · Duodenojejunal junction</t>
     </r>
   </si>
   <si>
@@ -27766,7 +27766,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Corkscrew / spring appearance</t>
+      <t xml:space="preserve">S18 · Corkscrew / spring appearance</t>
     </r>
   </si>
   <si>
@@ -27900,7 +27900,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Jejunal position</t>
+      <t xml:space="preserve">S18 · Jejunal position</t>
     </r>
   </si>
   <si>
@@ -28034,7 +28034,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Cecal position</t>
+      <t xml:space="preserve">S18 · Cecal position</t>
     </r>
   </si>
   <si>
@@ -28168,7 +28168,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Whole-gastrointestinal study</t>
+      <t xml:space="preserve">S18 · Whole-gastrointestinal study</t>
     </r>
   </si>
   <si>
@@ -28302,7 +28302,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 · Barium used</t>
+      <t xml:space="preserve">S18 · Barium used</t>
     </r>
   </si>
   <si>
@@ -28436,7 +28436,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S9 · </t>
+      <t xml:space="preserve">S8 · </t>
     </r>
     <r>
       <rPr>
@@ -28621,7 +28621,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S9 · </t>
+      <t xml:space="preserve">S8 · </t>
     </r>
     <r>
       <rPr>
@@ -28806,7 +28806,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S9 · </t>
+      <t xml:space="preserve">S8 · </t>
     </r>
     <r>
       <rPr>
@@ -28991,7 +28991,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S9 · </t>
+      <t xml:space="preserve">S8 · </t>
     </r>
     <r>
       <rPr>
@@ -29176,7 +29176,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S10 · D3 or duodenojejunal junction</t>
+      <t xml:space="preserve">S9 · D3 or duodenojejunal junction</t>
     </r>
   </si>
   <si>
@@ -29327,7 +29327,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S10 · Superior mesenteric artery–vein relationship</t>
+      <t xml:space="preserve">S9 · Superior mesenteric artery–vein relationship</t>
     </r>
   </si>
   <si>
@@ -29363,7 +29363,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S10 · Enteric fluid administration</t>
+      <t xml:space="preserve">S9 · Enteric fluid administration</t>
     </r>
   </si>
   <si>
@@ -29514,7 +29514,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S10 · Whirlpool, swirl or spiral appearance reported</t>
+      <t xml:space="preserve">S9 · Whirlpool, swirl or spiral appearance reported</t>
     </r>
   </si>
   <si>
@@ -29665,7 +29665,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S11 · Explicit operative statement of torsion,</t>
+      <t xml:space="preserve">S10 · Explicit operative statement of torsion,</t>
     </r>
   </si>
   <si>
@@ -29765,7 +29765,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S11 · Excluding children whose record states a</t>
+      <t xml:space="preserve">S10 · Excluding children whose record states a</t>
     </r>
   </si>
   <si>
@@ -29865,7 +29865,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S11 · Requiring a documented rotation of 360° </t>
+      <t xml:space="preserve">S10 · Requiring a documented rotation of 360° </t>
     </r>
   </si>
   <si>
@@ -29965,7 +29965,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S12 · Ultrasound, crude</t>
+      <t xml:space="preserve">S11 · Ultrasound, crude</t>
     </r>
   </si>
   <si>
@@ -30099,7 +30099,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S12 · Ultrasound, adjusted for great-vessel session</t>
+      <t xml:space="preserve">S11 · Ultrasound, adjusted for great-vessel session</t>
     </r>
   </si>
   <si>
@@ -30233,7 +30233,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S12 · CT, crude</t>
+      <t xml:space="preserve">S11 · CT, crude</t>
     </r>
   </si>
   <si>
@@ -30367,7 +30367,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S12 · CT, adjusted for contrast enhancement</t>
+      <t xml:space="preserve">S11 · CT, adjusted for contrast enhancement</t>
     </r>
   </si>
   <si>
@@ -30501,7 +30501,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S12 · UGI series, crude</t>
+      <t xml:space="preserve">S11 · UGI series, crude</t>
     </r>
   </si>
   <si>
@@ -30635,7 +30635,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S13 · UGI series vs CT</t>
+      <t xml:space="preserve">S12 · UGI series vs CT</t>
     </r>
   </si>
   <si>
@@ -30752,7 +30752,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S13 · UGI series vs ultrasound</t>
+      <t xml:space="preserve">S12 · UGI series vs ultrasound</t>
     </r>
   </si>
   <si>
@@ -30869,7 +30869,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S13 · CT vs ultrasound</t>
+      <t xml:space="preserve">S12 · CT vs ultrasound</t>
     </r>
   </si>
   <si>
@@ -30986,7 +30986,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S14 · UGI vs CT × </t>
+      <t xml:space="preserve">S13 · UGI vs CT × </t>
     </r>
     <r>
       <rPr>
@@ -31094,7 +31094,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S14 · </t>
+      <t xml:space="preserve">S13 · </t>
     </r>
     <r>
       <rPr>
@@ -31202,7 +31202,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S14 · Firth</t>
+      <t xml:space="preserve">S13 · Firth</t>
     </r>
   </si>
   <si>
@@ -31302,7 +31302,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S14 · </t>
+      <t xml:space="preserve">S13 · </t>
     </r>
     <r>
       <rPr>
@@ -31461,7 +31461,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S14 · CT </t>
+      <t xml:space="preserve">S13 · CT </t>
     </r>
     <r>
       <rPr>
@@ -31787,7 +31787,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S16 · Primary: final label</t>
+      <t xml:space="preserve">S14 · Primary: final label</t>
     </r>
   </si>
   <si>
@@ -31972,7 +31972,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S16 · Conclusion names malrotation</t>
+      <t xml:space="preserve">S14 · Conclusion names malrotation</t>
     </r>
   </si>
   <si>
@@ -32157,7 +32157,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S16 · Possible-tier conclusions counted negative</t>
+      <t xml:space="preserve">S14 · Possible-tier conclusions counted negative</t>
     </r>
   </si>
   <si>
@@ -32342,7 +32342,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S16 · Conclusion-only classifier (Supplement_1_classifier.py)</t>
+      <t xml:space="preserve">S14 · Conclusion-only classifier (Supplement_1_classifier.py)</t>
     </r>
   </si>
   <si>
@@ -32527,7 +32527,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S17 · Primary: final label</t>
+      <t xml:space="preserve">S15 · Primary: final label</t>
     </r>
   </si>
   <si>
@@ -32763,7 +32763,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S17 · Conclusion names malrotation</t>
+      <t xml:space="preserve">S15 · Conclusion names malrotation</t>
     </r>
   </si>
   <si>
@@ -32948,7 +32948,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S17 · Possible-tier conclusions counted negative</t>
+      <t xml:space="preserve">S15 · Possible-tier conclusions counted negative</t>
     </r>
   </si>
   <si>
@@ -33133,7 +33133,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S17 · Conclusion-only classifier (Supplement_1_classifier.py)</t>
+      <t xml:space="preserve">S15 · Conclusion-only classifier (Supplement_1_classifier.py)</t>
     </r>
   </si>
   <si>
@@ -33318,7 +33318,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Index examinations, n</t>
+      <t xml:space="preserve">S16 · Index examinations, n</t>
     </r>
   </si>
   <si>
@@ -33418,7 +33418,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Calendar days from index examination to operation, median (IQR)</t>
+      <t xml:space="preserve">S16 · Calendar days from index examination to operation, median (IQR)</t>
     </r>
   </si>
   <si>
@@ -33457,7 +33457,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Same day, n (%)</t>
+      <t xml:space="preserve">S16 · Same day, n (%)</t>
     </r>
   </si>
   <si>
@@ -33496,7 +33496,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · 1 day before, n (%)</t>
+      <t xml:space="preserve">S16 · 1 day before, n (%)</t>
     </r>
   </si>
   <si>
@@ -33535,7 +33535,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · 2–7 days before, n (%)</t>
+      <t xml:space="preserve">S16 · 2–7 days before, n (%)</t>
     </r>
   </si>
   <si>
@@ -33574,7 +33574,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · More than 7 days before, n (%)</t>
+      <t xml:space="preserve">S16 · More than 7 days before, n (%)</t>
     </r>
   </si>
   <si>
@@ -33613,7 +33613,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Detection, final label, closest episode (primary), n/N (%)</t>
+      <t xml:space="preserve">S16 · Detection, final label, closest episode (primary), n/N (%)</t>
     </r>
   </si>
   <si>
@@ -33652,7 +33652,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Detection, conclusion-only classifier, closest episode, n/N (%)</t>
+      <t xml:space="preserve">S16 · Detection, conclusion-only classifier, closest episode, n/N (%)</t>
     </r>
   </si>
   <si>
@@ -33691,7 +33691,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Detection, conclusion-only classifier, earliest episode, n/N (%)</t>
+      <t xml:space="preserve">S16 · Detection, conclusion-only classifier, earliest episode, n/N (%)</t>
     </r>
   </si>
   <si>
@@ -33730,7 +33730,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Detection, conclusion-only classifier, any preoperative episode positive, n/N (%)</t>
+      <t xml:space="preserve">S16 · Detection, conclusion-only classifier, any preoperative episode positive, n/N (%)</t>
     </r>
   </si>
   <si>
@@ -33769,7 +33769,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Children with more than one preoperative episode, n</t>
+      <t xml:space="preserve">S16 · Children with more than one preoperative episode, n</t>
     </r>
   </si>
   <si>
@@ -33808,7 +33808,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Detection, final label, examinations within 2 days of operation, n/N (%)</t>
+      <t xml:space="preserve">S16 · Detection, final label, examinations within 2 days of operation, n/N (%)</t>
     </r>
   </si>
   <si>
@@ -33847,7 +33847,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Adjusted OR vs UGI series, examinations within 2 days (95% CI)</t>
+      <t xml:space="preserve">S16 · Adjusted OR vs UGI series, examinations within 2 days (95% CI)</t>
     </r>
   </si>
   <si>
@@ -33886,7 +33886,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S18 · Adjusted OR vs CT, examinations within 2 days (95% CI)</t>
+      <t xml:space="preserve">S16 · Adjusted OR vs CT, examinations within 2 days (95% CI)</t>
     </r>
   </si>
   <si>
@@ -33925,7 +33925,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S19 · All ultrasound examinations (primary denominator)</t>
+      <t xml:space="preserve">S17 · All ultrasound examinations (primary denominator)</t>
     </r>
   </si>
   <si>
@@ -34093,7 +34093,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S19 · Booked as gastrointestinal</t>
+      <t xml:space="preserve">S17 · Booked as gastrointestinal</t>
     </r>
   </si>
   <si>
@@ -34261,7 +34261,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S19 · Booked as abdominal great-vessel</t>
+      <t xml:space="preserve">S17 · Booked as abdominal great-vessel</t>
     </r>
   </si>
   <si>
@@ -34429,7 +34429,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S19 · Booked as gastrointestinal or great-vessel</t>
+      <t xml:space="preserve">S17 · Booked as gastrointestinal or great-vessel</t>
     </r>
   </si>
   <si>
@@ -34597,7 +34597,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S19 · Booked as pyloric only</t>
+      <t xml:space="preserve">S17 · Booked as pyloric only</t>
     </r>
   </si>
   <si>
@@ -34765,7 +34765,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S19 · Performed at the bedside</t>
+      <t xml:space="preserve">S17 · Performed at the bedside</t>
     </r>
   </si>
   <si>
@@ -34933,7 +34933,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S19 · Child aged 28 days or younger</t>
+      <t xml:space="preserve">S17 · Child aged 28 days or younger</t>
     </r>
   </si>
   <si>
@@ -35340,7 +35340,7 @@
     <t xml:space="preserve">Title Page · Word count</t>
   </si>
   <si>
-    <t xml:space="preserve">2,976 … Abstract: 248 words</t>
+    <t xml:space="preserve">2,978 … Abstract: 248 words</t>
   </si>
   <si>
     <r>
@@ -35375,7 +35375,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2976</t>
+      <t xml:space="preserve">2978</t>
     </r>
     <r>
       <rPr>
@@ -35498,7 +35498,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Word count: 2,976 … Tables: 4; Figures: 3; Supplements 1–4</t>
+    <t xml:space="preserve">Word count: 2,978 … Tables: 4; Figures: 3; Supplements 1–4</t>
   </si>
   <si>
     <r>
@@ -35516,7 +35516,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2976</t>
+      <t xml:space="preserve">2978</t>
     </r>
   </si>
   <si>
@@ -38566,6 +38566,95 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">3 · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">正文（计数词）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> one</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">； </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">one in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">； </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">three CT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Two features</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">4 · A</t>
     </r>
     <r>
@@ -39545,7 +39634,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S8 </t>
+      <t xml:space="preserve">S18 </t>
     </r>
     <r>
       <rPr>
@@ -41386,7 +41475,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S9</t>
+      <t xml:space="preserve">S8</t>
     </r>
   </si>
   <si>
@@ -42176,7 +42265,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S9</t>
+      <t xml:space="preserve">S8</t>
     </r>
     <r>
       <rPr>
@@ -43057,7 +43146,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S15 </t>
+      <t xml:space="preserve">S19 </t>
     </r>
     <r>
       <rPr>
@@ -43656,7 +43745,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2 · S2.7–S2.10 </t>
+      <t xml:space="preserve">2 · S2.7–S2.9 </t>
     </r>
     <r>
       <rPr>
@@ -43673,7 +43762,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">S16–S19</t>
+      <t xml:space="preserve">S14–S17</t>
     </r>
     <r>
       <rPr>
@@ -45158,7 +45247,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(核对表!B2:B2000)</f>
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45203,7 +45292,7 @@
       </c>
       <c r="B26" s="6" t="n">
         <f aca="false">COUNTIF(核对表!C2:C2000,"【定义/描述性数字】*")</f>
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45231,7 +45320,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E355"/>
+  <dimension ref="A1:E356"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -49456,7 +49545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="8" t="s">
         <v>683</v>
       </c>
@@ -51242,7 +51331,7 @@
       </c>
     </row>
     <row r="354" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="11" t="s">
+      <c r="A354" s="10" t="s">
         <v>944</v>
       </c>
       <c r="B354" s="11" t="s">
@@ -51275,8 +51364,25 @@
         <v>32</v>
       </c>
     </row>
+    <row r="356" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="B356" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="C356" s="10" t="s">
+        <v>893</v>
+      </c>
+      <c r="D356" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E356" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E355"/>
+  <autoFilter ref="A1:E356"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -51305,7 +51411,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>23</v>
@@ -51350,66 +51456,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -51443,27 +51549,27 @@
         <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51471,13 +51577,13 @@
         <v>38</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51485,13 +51591,13 @@
         <v>134</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51499,13 +51605,13 @@
         <v>277</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51513,27 +51619,27 @@
         <v>283</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>984</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>982</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51541,27 +51647,27 @@
         <v>111</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>69</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51569,13 +51675,13 @@
         <v>127</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51583,13 +51689,13 @@
         <v>146</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51597,13 +51703,13 @@
         <v>368</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51611,13 +51717,13 @@
         <v>382</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51625,13 +51731,13 @@
         <v>385</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51639,13 +51745,13 @@
         <v>397</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51653,265 +51759,265 @@
         <v>406</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
   </sheetData>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -35340,7 +35340,7 @@
     <t xml:space="preserve">Title Page · Word count</t>
   </si>
   <si>
-    <t xml:space="preserve">2,978 … Abstract: 248 words</t>
+    <t xml:space="preserve">2,977 … Abstract: 248 words</t>
   </si>
   <si>
     <r>
@@ -35375,7 +35375,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2978</t>
+      <t xml:space="preserve">2977</t>
     </r>
     <r>
       <rPr>
@@ -35498,7 +35498,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Word count: 2,978 … Tables: 4; Figures: 3; Supplements 1–4</t>
+    <t xml:space="preserve">Word count: 2,977 … Tables: 4; Figures: 3; Supplements 1–4</t>
   </si>
   <si>
     <r>
@@ -35516,7 +35516,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2978</t>
+      <t xml:space="preserve">2977</t>
     </r>
   </si>
   <si>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -35335,7 +35335,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">all seven authors</t>
+    <t xml:space="preserve">all ten authors</t>
   </si>
   <si>
     <r>
@@ -35370,7 +35370,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">7 </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>

--- a/数字核对表.xlsx
+++ b/数字核对表.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">专项检查!$A$1:$B$8</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">更正记录!$A$1:$D$34</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$355</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">核对表!$A$1:$E$358</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">问题汇总!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="1088">
   <si>
     <r>
       <rPr>
@@ -37828,6 +37828,80 @@
       </rPr>
       <t xml:space="preserve">by two independent</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">supp1.md:21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（计数词）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">two written</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">supp1.md:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（计数词）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">two wordings</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">补充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 · E1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（计数词）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> two Chinese</t>
   </si>
   <si>
     <r>
@@ -45137,7 +45211,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(核对表!B2:B2000)</f>
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45182,7 +45256,7 @@
       </c>
       <c r="B26" s="6" t="n">
         <f aca="false">COUNTIF(核对表!C2:C2000,"【定义/描述性数字】*")</f>
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45210,7 +45284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E355"/>
+  <dimension ref="A1:E358"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -51051,7 +51125,7 @@
       </c>
     </row>
     <row r="344" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="10" t="s">
+      <c r="A344" s="11" t="s">
         <v>923</v>
       </c>
       <c r="B344" s="11" t="s">
@@ -51068,7 +51142,7 @@
       </c>
     </row>
     <row r="345" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="10" t="s">
+      <c r="A345" s="11" t="s">
         <v>925</v>
       </c>
       <c r="B345" s="11" t="s">
@@ -51221,7 +51295,7 @@
       </c>
     </row>
     <row r="354" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="11" t="s">
+      <c r="A354" s="10" t="s">
         <v>943</v>
       </c>
       <c r="B354" s="11" t="s">
@@ -51238,7 +51312,7 @@
       </c>
     </row>
     <row r="355" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="11" t="s">
+      <c r="A355" s="10" t="s">
         <v>945</v>
       </c>
       <c r="B355" s="11" t="s">
@@ -51254,8 +51328,59 @@
         <v>32</v>
       </c>
     </row>
+    <row r="356" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A356" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="B356" s="11" t="s">
+        <v>948</v>
+      </c>
+      <c r="C356" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="D356" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E356" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="11" t="s">
+        <v>949</v>
+      </c>
+      <c r="B357" s="11" t="s">
+        <v>950</v>
+      </c>
+      <c r="C357" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="D357" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E357" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="11" t="s">
+        <v>951</v>
+      </c>
+      <c r="B358" s="11" t="s">
+        <v>952</v>
+      </c>
+      <c r="C358" s="10" t="s">
+        <v>892</v>
+      </c>
+      <c r="D358" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E358" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E355"/>
+  <autoFilter ref="A1:E358"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -51284,7 +51409,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>23</v>
@@ -51329,66 +51454,66 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
     </row>
   </sheetData>
@@ -51422,27 +51547,27 @@
         <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>968</v>
+        <v>974</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51450,13 +51575,13 @@
         <v>38</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>973</v>
+        <v>979</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51464,13 +51589,13 @@
         <v>134</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>974</v>
+        <v>980</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>976</v>
+        <v>982</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51478,13 +51603,13 @@
         <v>282</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>978</v>
+        <v>984</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51492,27 +51617,27 @@
         <v>288</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>979</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51520,27 +51645,27 @@
         <v>111</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>986</v>
+        <v>992</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>69</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51548,13 +51673,13 @@
         <v>127</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51562,13 +51687,13 @@
         <v>146</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51576,13 +51701,13 @@
         <v>373</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51590,13 +51715,13 @@
         <v>387</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51604,13 +51729,13 @@
         <v>390</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51618,13 +51743,13 @@
         <v>402</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51632,265 +51757,265 @@
         <v>411</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="58.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="69.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
   </sheetData>
